--- a/Results_isofys/tessf.xlsx
+++ b/Results_isofys/tessf.xlsx
@@ -521,12 +521,12 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>mean toughness (kN/m)</t>
+          <t>force to punch (kN/m)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>mean thickness (mm)</t>
+          <t>thickness (mm)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">

--- a/Results_isofys/tessf.xlsx
+++ b/Results_isofys/tessf.xlsx
@@ -470,7 +470,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>[C]%</t>
+          <t>[C]</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>[C_b]%</t>
+          <t>[C_b]</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">

--- a/Results_isofys/tessf.xlsx
+++ b/Results_isofys/tessf.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH95"/>
+  <dimension ref="A1:AI95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -598,6 +598,11 @@
           <t>specie</t>
         </is>
       </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Specific leaf area (g/cm²)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -714,6 +719,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI2" t="n">
+        <v>34.15994277539342</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -830,6 +838,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI3" t="n">
+        <v>33.18294478527607</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -946,6 +957,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI4" t="n">
+        <v>37.93648208469055</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -1062,6 +1076,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI5" t="n">
+        <v>40.56470588235294</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -1178,6 +1195,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI6" t="n">
+        <v>35.25954751131221</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1294,6 +1314,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI7" t="n">
+        <v>33.15173383317713</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1410,6 +1433,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI8" t="n">
+        <v>30.50483754512636</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1526,6 +1552,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI9" t="n">
+        <v>40.07197898423818</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1642,6 +1671,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI10" t="n">
+        <v>25.14212910532276</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1758,6 +1790,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI11" t="n">
+        <v>34.10823136818687</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1874,6 +1909,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI12" t="n">
+        <v>43.40028169014084</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1990,6 +2028,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI13" t="n">
+        <v>35.8758865248227</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -2106,6 +2147,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI14" t="n">
+        <v>31.9693215339233</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -2222,6 +2266,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI15" t="n">
+        <v>32.25160202360878</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -2338,6 +2385,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI16" t="n">
+        <v>35.23089668615984</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -2454,6 +2504,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI17" t="n">
+        <v>34.03149664929263</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -2570,6 +2623,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI18" t="n">
+        <v>34.42013201320133</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -2686,6 +2742,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI19" t="n">
+        <v>37.13388601036269</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -2802,6 +2861,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI20" t="n">
+        <v>34.93205417607223</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -2918,6 +2980,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI21" t="n">
+        <v>38.12042253521127</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -3034,6 +3099,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI22" t="n">
+        <v>34.02602230483271</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -3150,6 +3218,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI23" t="n">
+        <v>36.02815442561206</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -3266,6 +3337,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI24" t="n">
+        <v>35.10835322195704</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -3382,6 +3456,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI25" t="n">
+        <v>32.21244286439817</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -3498,6 +3575,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI26" t="n">
+        <v>38.78301343570058</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -3614,6 +3694,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI27" t="n">
+        <v>35.49061855670104</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -3730,6 +3813,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI28" t="n">
+        <v>34.75611814345991</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -3846,6 +3932,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI29" t="n">
+        <v>34.20469107551487</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -3962,6 +4051,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI30" t="n">
+        <v>43.41372646184341</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -4078,6 +4170,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI31" t="n">
+        <v>43.41372646184341</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -4194,6 +4289,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI32" t="n">
+        <v>38.38884093711468</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -4310,6 +4408,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI33" t="n">
+        <v>28.00729765590447</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -4426,6 +4527,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI34" t="n">
+        <v>28.00729765590447</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -4542,6 +4646,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI35" t="n">
+        <v>37.72970873786407</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -4658,6 +4765,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI36" t="n">
+        <v>34.93055141579732</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -4774,6 +4884,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI37" t="n">
+        <v>31.18076158940397</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -4890,6 +5003,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI38" t="n">
+        <v>41.06741071428572</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -5006,6 +5122,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI39" t="n">
+        <v>37.32312049433573</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -5122,6 +5241,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI40" t="n">
+        <v>36.17970168612192</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -5238,6 +5360,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI41" t="n">
+        <v>32.91402805611222</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -5354,6 +5479,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI42" t="n">
+        <v>31.10285451197053</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -5470,6 +5598,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI43" t="n">
+        <v>30.39869888475836</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -5586,6 +5717,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI44" t="n">
+        <v>37.48323197219809</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -5702,6 +5836,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI45" t="n">
+        <v>32.09768</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -5818,6 +5955,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI46" t="n">
+        <v>32.09768</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -5934,6 +6074,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI47" t="n">
+        <v>39.16065382370111</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -6050,6 +6193,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI48" t="n">
+        <v>32.11846846846846</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -6166,6 +6312,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI49" t="n">
+        <v>38.09801840056618</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -6282,6 +6431,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI50" t="n">
+        <v>37.71034928848641</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -6398,6 +6550,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI51" t="n">
+        <v>39.72764811490126</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -6514,6 +6669,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI52" t="n">
+        <v>33.31036454610436</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -6630,6 +6788,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI53" t="n">
+        <v>34.7460815047022</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -6746,6 +6907,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI54" t="n">
+        <v>31.98261633011413</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -6862,6 +7026,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI55" t="n">
+        <v>38.49102196752626</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -6978,6 +7145,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI56" t="n">
+        <v>35.47107516650809</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -7094,6 +7264,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI57" t="n">
+        <v>32.22464912280702</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -7210,6 +7383,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI58" t="n">
+        <v>33.99637952559301</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -7326,6 +7502,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI59" t="n">
+        <v>33.4044665012407</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -7442,6 +7621,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI60" t="n">
+        <v>37.73743016759776</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -7558,6 +7740,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI61" t="n">
+        <v>37.00026553372279</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -7674,6 +7859,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI62" t="n">
+        <v>45.65359911406424</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -7790,6 +7978,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI63" t="n">
+        <v>31.62051282051283</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -7906,6 +8097,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI64" t="n">
+        <v>38.07644376899696</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -8022,6 +8216,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI65" t="n">
+        <v>34.4926213592233</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -8138,6 +8335,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI66" t="n">
+        <v>36.54322709163347</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -8254,6 +8454,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI67" t="n">
+        <v>36.84074074074074</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -8370,6 +8573,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI68" t="n">
+        <v>36.31700201207244</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -8486,6 +8692,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI69" t="n">
+        <v>33.07568366592757</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -8602,6 +8811,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI70" t="n">
+        <v>32.22326111744584</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -8718,6 +8930,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI71" t="n">
+        <v>36.82448866777225</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -8832,6 +9047,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI72" t="n">
+        <v>36.82448866777225</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -8946,6 +9164,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI73" t="n">
+        <v>37.93288288288289</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -9062,6 +9283,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI74" t="n">
+        <v>39.81607142857143</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -9178,6 +9402,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI75" t="n">
+        <v>38.9956570155902</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -9294,6 +9521,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI76" t="n">
+        <v>35.01108280254777</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -9410,6 +9640,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI77" t="n">
+        <v>35.7625352112676</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -9526,6 +9759,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI78" t="n">
+        <v>36.05222437137331</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -9642,6 +9878,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI79" t="n">
+        <v>29.2687074829932</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -9758,6 +9997,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI80" t="n">
+        <v>40.31574858757062</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -9874,6 +10116,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI81" t="n">
+        <v>32.95561719833564</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -9990,6 +10235,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI82" t="n">
+        <v>37.79894273127753</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -10106,6 +10354,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI83" t="n">
+        <v>31.78387096774194</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -10222,6 +10473,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI84" t="n">
+        <v>41.63273092369477</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -10338,6 +10592,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI85" t="n">
+        <v>32.12362911266202</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -10454,6 +10711,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI86" t="n">
+        <v>39.07777777777778</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -10570,6 +10830,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI87" t="n">
+        <v>34.49588744588745</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -10686,6 +10949,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI88" t="n">
+        <v>43.50616113744076</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -10802,6 +11068,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI89" t="n">
+        <v>41.68621562952244</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -10918,6 +11187,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI90" t="n">
+        <v>35.96792650918635</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -11034,6 +11306,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI91" t="n">
+        <v>34.36061538461539</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -11150,6 +11425,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI92" t="n">
+        <v>35.34196357878068</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -11266,6 +11544,9 @@
           <t>lojaensis</t>
         </is>
       </c>
+      <c r="AI93" t="n">
+        <v>38.64987714987715</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -11382,6 +11663,9 @@
           <t>sp nov</t>
         </is>
       </c>
+      <c r="AI94" t="n">
+        <v>30.17824074074074</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -11493,6 +11777,9 @@
         <is>
           <t>lojaensis</t>
         </is>
+      </c>
+      <c r="AI95" t="n">
+        <v>39.28316008316008</v>
       </c>
     </row>
   </sheetData>

--- a/Results_isofys/tessf.xlsx
+++ b/Results_isofys/tessf.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI95"/>
+  <dimension ref="A1:AH95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -598,11 +598,6 @@
           <t>specie</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Specific leaf area (g/cm²)</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -719,9 +714,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI2" t="n">
-        <v>34.15994277539342</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -838,9 +830,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI3" t="n">
-        <v>33.18294478527607</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -957,9 +946,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI4" t="n">
-        <v>37.93648208469055</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -1076,9 +1062,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI5" t="n">
-        <v>40.56470588235294</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -1195,9 +1178,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI6" t="n">
-        <v>35.25954751131221</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1314,9 +1294,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI7" t="n">
-        <v>33.15173383317713</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1433,9 +1410,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI8" t="n">
-        <v>30.50483754512636</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1552,9 +1526,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI9" t="n">
-        <v>40.07197898423818</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1671,9 +1642,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI10" t="n">
-        <v>25.14212910532276</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1790,9 +1758,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI11" t="n">
-        <v>34.10823136818687</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1909,9 +1874,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI12" t="n">
-        <v>43.40028169014084</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -2028,9 +1990,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI13" t="n">
-        <v>35.8758865248227</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -2147,9 +2106,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI14" t="n">
-        <v>31.9693215339233</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -2266,9 +2222,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI15" t="n">
-        <v>32.25160202360878</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -2385,9 +2338,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI16" t="n">
-        <v>35.23089668615984</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -2504,9 +2454,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI17" t="n">
-        <v>34.03149664929263</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -2623,9 +2570,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI18" t="n">
-        <v>34.42013201320133</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -2742,9 +2686,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI19" t="n">
-        <v>37.13388601036269</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -2861,9 +2802,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI20" t="n">
-        <v>34.93205417607223</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -2980,9 +2918,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI21" t="n">
-        <v>38.12042253521127</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -3099,9 +3034,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI22" t="n">
-        <v>34.02602230483271</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -3218,9 +3150,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI23" t="n">
-        <v>36.02815442561206</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -3337,9 +3266,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI24" t="n">
-        <v>35.10835322195704</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -3456,9 +3382,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI25" t="n">
-        <v>32.21244286439817</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -3575,9 +3498,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI26" t="n">
-        <v>38.78301343570058</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -3694,9 +3614,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI27" t="n">
-        <v>35.49061855670104</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -3813,9 +3730,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI28" t="n">
-        <v>34.75611814345991</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -3932,9 +3846,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI29" t="n">
-        <v>34.20469107551487</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -4051,9 +3962,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI30" t="n">
-        <v>43.41372646184341</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -4170,9 +4078,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI31" t="n">
-        <v>43.41372646184341</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -4289,9 +4194,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI32" t="n">
-        <v>38.38884093711468</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -4408,9 +4310,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI33" t="n">
-        <v>28.00729765590447</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -4527,9 +4426,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI34" t="n">
-        <v>28.00729765590447</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -4646,9 +4542,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI35" t="n">
-        <v>37.72970873786407</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -4765,9 +4658,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI36" t="n">
-        <v>34.93055141579732</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -4884,9 +4774,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI37" t="n">
-        <v>31.18076158940397</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -5003,9 +4890,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI38" t="n">
-        <v>41.06741071428572</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -5122,9 +5006,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI39" t="n">
-        <v>37.32312049433573</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -5241,9 +5122,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI40" t="n">
-        <v>36.17970168612192</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -5360,9 +5238,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI41" t="n">
-        <v>32.91402805611222</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -5479,9 +5354,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI42" t="n">
-        <v>31.10285451197053</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -5598,9 +5470,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI43" t="n">
-        <v>30.39869888475836</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -5717,9 +5586,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI44" t="n">
-        <v>37.48323197219809</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -5836,9 +5702,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI45" t="n">
-        <v>32.09768</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -5955,9 +5818,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI46" t="n">
-        <v>32.09768</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -6074,9 +5934,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI47" t="n">
-        <v>39.16065382370111</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -6193,9 +6050,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI48" t="n">
-        <v>32.11846846846846</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -6312,9 +6166,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI49" t="n">
-        <v>38.09801840056618</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -6431,9 +6282,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI50" t="n">
-        <v>37.71034928848641</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -6550,9 +6398,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI51" t="n">
-        <v>39.72764811490126</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -6669,9 +6514,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI52" t="n">
-        <v>33.31036454610436</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -6788,9 +6630,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI53" t="n">
-        <v>34.7460815047022</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -6907,9 +6746,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI54" t="n">
-        <v>31.98261633011413</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -7026,9 +6862,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI55" t="n">
-        <v>38.49102196752626</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -7145,9 +6978,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI56" t="n">
-        <v>35.47107516650809</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -7264,9 +7094,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI57" t="n">
-        <v>32.22464912280702</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -7383,9 +7210,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI58" t="n">
-        <v>33.99637952559301</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -7502,9 +7326,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI59" t="n">
-        <v>33.4044665012407</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -7621,9 +7442,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI60" t="n">
-        <v>37.73743016759776</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -7740,9 +7558,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI61" t="n">
-        <v>37.00026553372279</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -7859,9 +7674,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI62" t="n">
-        <v>45.65359911406424</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -7978,9 +7790,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI63" t="n">
-        <v>31.62051282051283</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -8097,9 +7906,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI64" t="n">
-        <v>38.07644376899696</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -8216,9 +8022,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI65" t="n">
-        <v>34.4926213592233</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -8335,9 +8138,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI66" t="n">
-        <v>36.54322709163347</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -8454,9 +8254,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI67" t="n">
-        <v>36.84074074074074</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -8573,9 +8370,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI68" t="n">
-        <v>36.31700201207244</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -8692,9 +8486,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI69" t="n">
-        <v>33.07568366592757</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -8811,9 +8602,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI70" t="n">
-        <v>32.22326111744584</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -8930,9 +8718,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI71" t="n">
-        <v>36.82448866777225</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -9047,9 +8832,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI72" t="n">
-        <v>36.82448866777225</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -9164,9 +8946,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI73" t="n">
-        <v>37.93288288288289</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -9283,9 +9062,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI74" t="n">
-        <v>39.81607142857143</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -9402,9 +9178,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI75" t="n">
-        <v>38.9956570155902</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -9521,9 +9294,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI76" t="n">
-        <v>35.01108280254777</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -9640,9 +9410,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI77" t="n">
-        <v>35.7625352112676</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -9759,9 +9526,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI78" t="n">
-        <v>36.05222437137331</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -9878,9 +9642,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI79" t="n">
-        <v>29.2687074829932</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -9997,9 +9758,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI80" t="n">
-        <v>40.31574858757062</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -10116,9 +9874,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI81" t="n">
-        <v>32.95561719833564</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -10235,9 +9990,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI82" t="n">
-        <v>37.79894273127753</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -10354,9 +10106,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI83" t="n">
-        <v>31.78387096774194</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -10473,9 +10222,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI84" t="n">
-        <v>41.63273092369477</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -10592,9 +10338,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI85" t="n">
-        <v>32.12362911266202</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -10711,9 +10454,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI86" t="n">
-        <v>39.07777777777778</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -10830,9 +10570,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI87" t="n">
-        <v>34.49588744588745</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -10949,9 +10686,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI88" t="n">
-        <v>43.50616113744076</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -11068,9 +10802,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI89" t="n">
-        <v>41.68621562952244</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -11187,9 +10918,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI90" t="n">
-        <v>35.96792650918635</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -11306,9 +11034,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI91" t="n">
-        <v>34.36061538461539</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -11425,9 +11150,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI92" t="n">
-        <v>35.34196357878068</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -11544,9 +11266,6 @@
           <t>lojaensis</t>
         </is>
       </c>
-      <c r="AI93" t="n">
-        <v>38.64987714987715</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -11663,9 +11382,6 @@
           <t>sp nov</t>
         </is>
       </c>
-      <c r="AI94" t="n">
-        <v>30.17824074074074</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -11777,9 +11493,6 @@
         <is>
           <t>lojaensis</t>
         </is>
-      </c>
-      <c r="AI95" t="n">
-        <v>39.28316008316008</v>
       </c>
     </row>
   </sheetData>

--- a/Results_isofys/tessf.xlsx
+++ b/Results_isofys/tessf.xlsx
@@ -613,10 +613,8 @@
           <t>592012</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>88</v>
@@ -734,10 +732,8 @@
           <t>592033</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C3" t="n">
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>8386</v>
@@ -855,10 +851,8 @@
           <t>592031</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>9096</v>
@@ -976,10 +970,8 @@
           <t>592251</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="C5" t="n">
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>721</v>
@@ -1097,10 +1089,8 @@
           <t>592151</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="C6" t="n">
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>7994</v>
@@ -1218,10 +1208,8 @@
           <t>592379</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="C7" t="n">
+        <v>19</v>
       </c>
       <c r="D7" t="n">
         <v>795</v>
@@ -1339,10 +1327,8 @@
           <t>592333</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="C8" t="n">
+        <v>17</v>
       </c>
       <c r="D8" t="n">
         <v>881</v>
@@ -1460,10 +1446,8 @@
           <t>592305</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="C9" t="n">
+        <v>14</v>
       </c>
       <c r="D9" t="n">
         <v>693</v>
@@ -1581,10 +1565,8 @@
           <t>592315</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="C10" t="n">
+        <v>16</v>
       </c>
       <c r="D10" t="n">
         <v>740</v>
@@ -1702,10 +1684,8 @@
           <t>592052</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C11" t="n">
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>8384</v>
@@ -1823,10 +1803,8 @@
           <t>592353</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="C12" t="n">
+        <v>17</v>
       </c>
       <c r="D12" t="n">
         <v>8954</v>
@@ -1944,10 +1922,8 @@
           <t>592324</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="C13" t="n">
+        <v>16</v>
       </c>
       <c r="D13" t="n">
         <v>764</v>
@@ -2065,10 +2041,8 @@
           <t>592339</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="C14" t="n">
+        <v>17</v>
       </c>
       <c r="D14" t="n">
         <v>4955</v>
@@ -2186,10 +2160,8 @@
           <t>592129</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="C15" t="n">
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>7645</v>
@@ -2307,10 +2279,8 @@
           <t>592101</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C16" t="n">
+        <v>4</v>
       </c>
       <c r="D16" t="n">
         <v>6021</v>
@@ -2428,10 +2398,8 @@
           <t>592115</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="C17" t="n">
+        <v>6</v>
       </c>
       <c r="D17" t="n">
         <v>205</v>
@@ -2549,10 +2517,8 @@
           <t>592065</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C18" t="n">
+        <v>3</v>
       </c>
       <c r="D18" t="n">
         <v>4898</v>
@@ -2670,10 +2636,8 @@
           <t>592180</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="C19" t="n">
+        <v>8</v>
       </c>
       <c r="D19" t="n">
         <v>8381</v>
@@ -2791,10 +2755,8 @@
           <t>592225</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C20" t="n">
+        <v>11</v>
       </c>
       <c r="D20" t="n">
         <v>9090</v>
@@ -2912,10 +2874,8 @@
           <t>592156</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="C21" t="n">
+        <v>8</v>
       </c>
       <c r="D21" t="n">
         <v>9080</v>
@@ -3033,10 +2993,8 @@
           <t>592293</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="C22" t="n">
+        <v>14</v>
       </c>
       <c r="D22" t="n">
         <v>580</v>
@@ -3154,10 +3112,8 @@
           <t>592141</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="C23" t="n">
+        <v>7</v>
       </c>
       <c r="D23" t="n">
         <v>378</v>
@@ -3275,10 +3231,8 @@
           <t>592087</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C24" t="n">
+        <v>3</v>
       </c>
       <c r="D24" t="n">
         <v>9738</v>
@@ -3396,10 +3350,8 @@
           <t>592041</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C25" t="n">
+        <v>2</v>
       </c>
       <c r="D25" t="n">
         <v>356</v>
@@ -3517,10 +3469,8 @@
           <t>592043</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C26" t="n">
+        <v>2</v>
       </c>
       <c r="D26" t="n">
         <v>172</v>
@@ -3638,10 +3588,8 @@
           <t>592064</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C27" t="n">
+        <v>3</v>
       </c>
       <c r="D27" t="n">
         <v>9084</v>
@@ -3759,10 +3707,8 @@
           <t>592046</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C28" t="n">
+        <v>2</v>
       </c>
       <c r="D28" t="n">
         <v>254</v>
@@ -3880,10 +3826,8 @@
           <t>592046</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C29" t="n">
+        <v>2</v>
       </c>
       <c r="D29" t="n">
         <v>8396</v>
@@ -4001,10 +3945,8 @@
           <t>592004</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C30" t="n">
+        <v>1</v>
       </c>
       <c r="D30" t="n">
         <v>7924</v>
@@ -4122,10 +4064,8 @@
           <t>592037</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C31" t="n">
+        <v>2</v>
       </c>
       <c r="D31" t="n">
         <v>7924</v>
@@ -4243,10 +4183,8 @@
           <t>592037</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C32" t="n">
+        <v>2</v>
       </c>
       <c r="D32" t="n">
         <v>69</v>
@@ -4364,10 +4302,8 @@
           <t>592073</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C33" t="n">
+        <v>3</v>
       </c>
       <c r="D33" t="n">
         <v>7922</v>
@@ -4485,10 +4421,8 @@
           <t>592227</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C34" t="n">
+        <v>11</v>
       </c>
       <c r="D34" t="n">
         <v>7922</v>
@@ -4606,10 +4540,8 @@
           <t>592223</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C35" t="n">
+        <v>11</v>
       </c>
       <c r="D35" t="n">
         <v>141</v>
@@ -4727,10 +4659,8 @@
           <t>592231</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C36" t="n">
+        <v>11</v>
       </c>
       <c r="D36" t="n">
         <v>587</v>
@@ -4848,10 +4778,8 @@
           <t>592273</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="C37" t="n">
+        <v>13</v>
       </c>
       <c r="D37" t="n">
         <v>575</v>
@@ -4969,10 +4897,8 @@
           <t>592269</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="C38" t="n">
+        <v>13</v>
       </c>
       <c r="D38" t="n">
         <v>596</v>
@@ -5090,10 +5016,8 @@
           <t>592299</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="C39" t="n">
+        <v>14</v>
       </c>
       <c r="D39" t="n">
         <v>631</v>
@@ -5211,10 +5135,8 @@
           <t>592105</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C40" t="n">
+        <v>4</v>
       </c>
       <c r="D40" t="n">
         <v>4445</v>
@@ -5332,10 +5254,8 @@
           <t>592220</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C41" t="n">
+        <v>11</v>
       </c>
       <c r="D41" t="n">
         <v>6976</v>
@@ -5453,10 +5373,8 @@
           <t>592198</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C42" t="n">
+        <v>9</v>
       </c>
       <c r="D42" t="n">
         <v>213</v>
@@ -5574,10 +5492,8 @@
           <t>592092</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C43" t="n">
+        <v>4</v>
       </c>
       <c r="D43" t="n">
         <v>569</v>
@@ -5695,10 +5611,8 @@
           <t>592092</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C44" t="n">
+        <v>4</v>
       </c>
       <c r="D44" t="n">
         <v>8361</v>
@@ -5816,10 +5730,8 @@
           <t>592206</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C45" t="n">
+        <v>9</v>
       </c>
       <c r="D45" t="n">
         <v>191</v>
@@ -5937,10 +5849,8 @@
           <t>592249</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="C46" t="n">
+        <v>12</v>
       </c>
       <c r="D46" t="n">
         <v>191</v>
@@ -6058,10 +5968,8 @@
           <t>592162</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="C47" t="n">
+        <v>8</v>
       </c>
       <c r="D47" t="n">
         <v>4469</v>
@@ -6179,10 +6087,8 @@
           <t>592317</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="C48" t="n">
+        <v>16</v>
       </c>
       <c r="D48" t="n">
         <v>4894</v>
@@ -6300,10 +6206,8 @@
           <t>592323</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="C49" t="n">
+        <v>16</v>
       </c>
       <c r="D49" t="n">
         <v>389</v>
@@ -6421,10 +6325,8 @@
           <t>592325</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="C50" t="n">
+        <v>16</v>
       </c>
       <c r="D50" t="n">
         <v>746</v>
@@ -6542,10 +6444,8 @@
           <t>592365</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C51" t="n">
+        <v>18</v>
       </c>
       <c r="D51" t="n">
         <v>763</v>
@@ -6663,10 +6563,8 @@
           <t>592344</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="C52" t="n">
+        <v>17</v>
       </c>
       <c r="D52" t="n">
         <v>768</v>
@@ -6784,10 +6682,8 @@
           <t>592359</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C53" t="n">
+        <v>18</v>
       </c>
       <c r="D53" t="n">
         <v>4940</v>
@@ -6905,10 +6801,8 @@
           <t>592246</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="C54" t="n">
+        <v>12</v>
       </c>
       <c r="D54" t="n">
         <v>902</v>
@@ -7026,10 +6920,8 @@
           <t>592005</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C55" t="n">
+        <v>1</v>
       </c>
       <c r="D55" t="n">
         <v>5880</v>
@@ -7147,10 +7039,8 @@
           <t>592132</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="C56" t="n">
+        <v>7</v>
       </c>
       <c r="D56" t="n">
         <v>708</v>
@@ -7268,10 +7158,8 @@
           <t>592361</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C57" t="n">
+        <v>18</v>
       </c>
       <c r="D57" t="n">
         <v>5812</v>
@@ -7389,10 +7277,8 @@
           <t>592074</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C58" t="n">
+        <v>3</v>
       </c>
       <c r="D58" t="n">
         <v>333</v>
@@ -7510,10 +7396,8 @@
           <t>592334</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="C59" t="n">
+        <v>17</v>
       </c>
       <c r="D59" t="n">
         <v>816</v>
@@ -7631,10 +7515,8 @@
           <t>592016</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C60" t="n">
+        <v>1</v>
       </c>
       <c r="D60" t="n">
         <v>143</v>
@@ -7752,10 +7634,8 @@
           <t>592253</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="C61" t="n">
+        <v>12</v>
       </c>
       <c r="D61" t="n">
         <v>4932</v>
@@ -7873,10 +7753,8 @@
           <t>592139</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="C62" t="n">
+        <v>7</v>
       </c>
       <c r="D62" t="n">
         <v>96</v>
@@ -7994,10 +7872,8 @@
           <t>592014</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C63" t="n">
+        <v>1</v>
       </c>
       <c r="D63" t="n">
         <v>729</v>
@@ -8115,10 +7991,8 @@
           <t>592136</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="C64" t="n">
+        <v>7</v>
       </c>
       <c r="D64" t="n">
         <v>6992</v>
@@ -8236,10 +8110,8 @@
           <t>592377</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="C65" t="n">
+        <v>19</v>
       </c>
       <c r="D65" t="n">
         <v>90</v>
@@ -8357,10 +8229,8 @@
           <t>592368</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C66" t="n">
+        <v>18</v>
       </c>
       <c r="D66" t="n">
         <v>341</v>
@@ -8478,10 +8348,8 @@
           <t>592320</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="C67" t="n">
+        <v>16</v>
       </c>
       <c r="D67" t="n">
         <v>4952</v>
@@ -8599,10 +8467,8 @@
           <t>592351</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="C68" t="n">
+        <v>17</v>
       </c>
       <c r="D68" t="n">
         <v>7578</v>
@@ -8720,10 +8586,8 @@
           <t>592172</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="C69" t="n">
+        <v>8</v>
       </c>
       <c r="D69" t="n">
         <v>755</v>
@@ -8841,10 +8705,8 @@
           <t>592172</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="C70" t="n">
+        <v>8</v>
       </c>
       <c r="D70" t="n">
         <v>4933</v>
@@ -8962,10 +8824,8 @@
           <t>592124</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="C71" t="n">
+        <v>6</v>
       </c>
       <c r="D71" t="n">
         <v>410</v>
@@ -9083,10 +8943,8 @@
           <t>592118</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="C72" t="n">
+        <v>6</v>
       </c>
       <c r="D72" t="n">
         <v>410</v>
@@ -9202,10 +9060,8 @@
           <t>592097</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C73" t="n">
+        <v>4</v>
       </c>
       <c r="D73" t="n">
         <v>310</v>
@@ -9321,10 +9177,8 @@
           <t>592235</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C74" t="n">
+        <v>11</v>
       </c>
       <c r="D74" t="n">
         <v>290</v>
@@ -9442,10 +9296,8 @@
           <t>592123</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="C75" t="n">
+        <v>6</v>
       </c>
       <c r="D75" t="n">
         <v>200</v>
@@ -9563,10 +9415,8 @@
           <t>592107</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C76" t="n">
+        <v>4</v>
       </c>
       <c r="D76" t="n">
         <v>915</v>
@@ -9684,10 +9534,8 @@
           <t>592108</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C77" t="n">
+        <v>4</v>
       </c>
       <c r="D77" t="n">
         <v>4905</v>
@@ -9805,10 +9653,8 @@
           <t>592055</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C78" t="n">
+        <v>2</v>
       </c>
       <c r="D78" t="n">
         <v>5807</v>
@@ -9926,10 +9772,8 @@
           <t>592277</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="C79" t="n">
+        <v>13</v>
       </c>
       <c r="D79" t="n">
         <v>219</v>
@@ -10047,10 +9891,8 @@
           <t>592117</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="C80" t="n">
+        <v>6</v>
       </c>
       <c r="D80" t="n">
         <v>267</v>
@@ -10168,10 +10010,8 @@
           <t>592250</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="C81" t="n">
+        <v>12</v>
       </c>
       <c r="D81" t="n">
         <v>642</v>
@@ -10289,10 +10129,8 @@
           <t>592148</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="C82" t="n">
+        <v>7</v>
       </c>
       <c r="D82" t="n">
         <v>286</v>
@@ -10410,10 +10248,8 @@
           <t>592015</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C83" t="n">
+        <v>1</v>
       </c>
       <c r="D83" t="n">
         <v>7594</v>
@@ -10531,10 +10367,8 @@
           <t>592133</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="C84" t="n">
+        <v>7</v>
       </c>
       <c r="D84" t="n">
         <v>6994</v>
@@ -10652,10 +10486,8 @@
           <t>592286</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="C85" t="n">
+        <v>13</v>
       </c>
       <c r="D85" t="n">
         <v>92</v>
@@ -10773,10 +10605,8 @@
           <t>592079</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C86" t="n">
+        <v>3</v>
       </c>
       <c r="D86" t="n">
         <v>335</v>
@@ -10894,10 +10724,8 @@
           <t>592019</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C87" t="n">
+        <v>1</v>
       </c>
       <c r="D87" t="n">
         <v>9742</v>
@@ -11015,10 +10843,8 @@
           <t>592103</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C88" t="n">
+        <v>4</v>
       </c>
       <c r="D88" t="n">
         <v>155</v>
@@ -11136,10 +10962,8 @@
           <t>592294</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="C89" t="n">
+        <v>14</v>
       </c>
       <c r="D89" t="n">
         <v>101</v>
@@ -11257,10 +11081,8 @@
           <t>592091</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C90" t="n">
+        <v>4</v>
       </c>
       <c r="D90" t="n">
         <v>209</v>
@@ -11378,10 +11200,8 @@
           <t>592302</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="C91" t="n">
+        <v>14</v>
       </c>
       <c r="D91" t="n">
         <v>666</v>
@@ -11499,10 +11319,8 @@
           <t>592272</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="C92" t="n">
+        <v>13</v>
       </c>
       <c r="D92" t="n">
         <v>188</v>
@@ -11620,10 +11438,8 @@
           <t>592029</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C93" t="n">
+        <v>1</v>
       </c>
       <c r="D93" t="n">
         <v>685</v>
@@ -11741,10 +11557,8 @@
           <t>592291</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="C94" t="n">
+        <v>14</v>
       </c>
       <c r="D94" t="n">
         <v>627</v>
@@ -11862,10 +11676,8 @@
           <t>592158</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="C95" t="n">
+        <v>8</v>
       </c>
       <c r="D95" t="n">
         <v>9091</v>

--- a/Results_isofys/tessf.xlsx
+++ b/Results_isofys/tessf.xlsx
@@ -429,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI95"/>
+  <dimension ref="A1:AI97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>sample-ID</t>
+          <t>code</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>genus</t>
+          <t>plot/tree</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
@@ -613,11 +613,15 @@
           <t>592012</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>88</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -714,12 +718,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>1C-88</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -732,11 +736,15 @@
           <t>592033</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>8386</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8386</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -833,12 +841,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>2P-8386</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -851,11 +859,15 @@
           <t>592031</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>9096</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>9096</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -952,12 +964,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>1C-9096</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -970,11 +982,15 @@
           <t>592251</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>12</v>
-      </c>
-      <c r="D5" t="n">
-        <v>721</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>721</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1071,12 +1087,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>12C-721</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -1089,11 +1105,15 @@
           <t>592151</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>7</v>
-      </c>
-      <c r="D6" t="n">
-        <v>7994</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7994</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1190,12 +1210,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>7C-7994</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -1208,11 +1228,15 @@
           <t>592379</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>19</v>
-      </c>
-      <c r="D7" t="n">
-        <v>795</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>795</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1309,12 +1333,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>19N-795</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -1327,11 +1351,15 @@
           <t>592333</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>17</v>
-      </c>
-      <c r="D8" t="n">
-        <v>881</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1428,12 +1456,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>17C-881</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -1446,11 +1474,15 @@
           <t>592305</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>14</v>
-      </c>
-      <c r="D9" t="n">
-        <v>693</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>693</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1547,12 +1579,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>14NP-693</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -1565,11 +1597,15 @@
           <t>592315</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>16</v>
-      </c>
-      <c r="D10" t="n">
-        <v>740</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1666,12 +1702,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>16P-740</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -1684,11 +1720,15 @@
           <t>592052</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>8384</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8384</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1785,12 +1825,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>2P-8384</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -1803,11 +1843,15 @@
           <t>592353</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>17</v>
-      </c>
-      <c r="D12" t="n">
-        <v>8954</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8954</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1904,12 +1948,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>17C-8954</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -1922,11 +1966,15 @@
           <t>592324</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>16</v>
-      </c>
-      <c r="D13" t="n">
-        <v>764</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2023,12 +2071,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>16P-764</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -2038,14 +2086,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>592339</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>17</v>
-      </c>
-      <c r="D14" t="n">
-        <v>4955</v>
+          <t>592378</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4955</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2054,32 +2106,32 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.4696</v>
+        <v>0.4569</v>
       </c>
       <c r="H14" t="n">
-        <v>30.46</v>
+        <v>29.86</v>
       </c>
       <c r="I14" t="n">
-        <v>43.54</v>
+        <v>45.86</v>
       </c>
       <c r="J14" t="n">
-        <v>-25.42</v>
+        <v>-25.01</v>
       </c>
       <c r="K14" t="n">
-        <v>0.007641264935176849</v>
+        <v>0.01416640448410562</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4780136056295743</v>
+        <v>0.5028190223614107</v>
       </c>
       <c r="M14" t="n">
-        <v>-6.661280589551962</v>
+        <v>-1.450948753137248</v>
       </c>
       <c r="N14" t="n">
-        <v>-28.06456223636443</v>
+        <v>-27.76316891782654</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -2142,12 +2194,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>19N-4955</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -2157,48 +2209,52 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>592129</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D15" t="n">
-        <v>7645</v>
+          <t>592339</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Myrcia sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.2281</v>
+        <v>0.4696</v>
       </c>
       <c r="H15" t="n">
-        <v>31.62</v>
+        <v>30.46</v>
       </c>
       <c r="I15" t="n">
-        <v>22.15</v>
+        <v>43.54</v>
       </c>
       <c r="J15" t="n">
-        <v>-27.37</v>
+        <v>-25.42</v>
       </c>
       <c r="K15" t="n">
-        <v>0.009749098546270586</v>
+        <v>0.007641264935176849</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4697587529355447</v>
+        <v>0.4780136056295743</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.585667233687743</v>
+        <v>-6.661280589551962</v>
       </c>
       <c r="N15" t="n">
-        <v>-31.21460853334117</v>
+        <v>-28.06456223636443</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -2261,12 +2317,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>17C-7645</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -2276,14 +2332,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>592101</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" t="n">
-        <v>6021</v>
+          <t>592129</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6021</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -2292,32 +2352,32 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.2738</v>
+        <v>0.2281</v>
       </c>
       <c r="H16" t="n">
-        <v>31.24</v>
+        <v>31.62</v>
       </c>
       <c r="I16" t="n">
-        <v>25.6</v>
+        <v>22.15</v>
       </c>
       <c r="J16" t="n">
-        <v>-27.22</v>
+        <v>-27.37</v>
       </c>
       <c r="K16" t="n">
-        <v>0.009505230483306095</v>
+        <v>0.009749098546270586</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4610071483677964</v>
+        <v>0.4697587529355447</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.46106590233417</v>
+        <v>-3.585667233687743</v>
       </c>
       <c r="N16" t="n">
-        <v>-30.41737459398286</v>
+        <v>-31.21460853334117</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -2380,12 +2440,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>6N-6021</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -2395,14 +2455,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>592115</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>6</v>
-      </c>
-      <c r="D17" t="n">
-        <v>205</v>
+          <t>592101</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -2411,32 +2475,32 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.5004</v>
+        <v>0.2738</v>
       </c>
       <c r="H17" t="n">
-        <v>30.57</v>
+        <v>31.24</v>
       </c>
       <c r="I17" t="n">
-        <v>40.42</v>
+        <v>25.6</v>
       </c>
       <c r="J17" t="n">
-        <v>-26.7</v>
+        <v>-27.22</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0111398212267561</v>
+        <v>0.009505230483306095</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4688268358720476</v>
+        <v>0.4610071483677964</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.756060999540157</v>
+        <v>-1.46106590233417</v>
       </c>
       <c r="N17" t="n">
-        <v>-29.98959052896133</v>
+        <v>-30.41737459398286</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -2499,12 +2563,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>4NP-205</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -2514,14 +2578,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>592065</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>4898</v>
+          <t>592222</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4898</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -2530,32 +2598,32 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.4964</v>
+        <v>0.5027</v>
       </c>
       <c r="H18" t="n">
-        <v>35.93</v>
+        <v>31.84</v>
       </c>
       <c r="I18" t="n">
-        <v>43.25</v>
+        <v>41.21</v>
       </c>
       <c r="J18" t="n">
-        <v>-28.06</v>
+        <v>-27.25</v>
       </c>
       <c r="K18" t="n">
-        <v>0.009043569810587505</v>
+        <v>0.009888404254099845</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4697706118710646</v>
+        <v>0.4827920143618233</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.444027144930838</v>
+        <v>-3.11016122143242</v>
       </c>
       <c r="N18" t="n">
-        <v>-30.88404811946089</v>
+        <v>-30.39792986375461</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -2618,12 +2686,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>11P-4898</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -2633,14 +2701,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>592180</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>8</v>
-      </c>
-      <c r="D19" t="n">
-        <v>8381</v>
+          <t>592115</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8381</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -2649,32 +2721,32 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.5157</v>
+        <v>0.5004</v>
       </c>
       <c r="H19" t="n">
-        <v>31.12</v>
+        <v>30.57</v>
       </c>
       <c r="I19" t="n">
-        <v>42.89</v>
+        <v>40.42</v>
       </c>
       <c r="J19" t="n">
-        <v>-28.34</v>
+        <v>-26.7</v>
       </c>
       <c r="K19" t="n">
-        <v>0.008368364062059925</v>
+        <v>0.0111398212267561</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4654813415219559</v>
+        <v>0.4688268358720476</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.858830262004631</v>
+        <v>-2.756060999540157</v>
       </c>
       <c r="N19" t="n">
-        <v>-31.39933347050956</v>
+        <v>-29.98959052896133</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -2737,12 +2809,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>6N-8381</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2824,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>592225</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>11</v>
-      </c>
-      <c r="D20" t="n">
-        <v>9090</v>
+          <t>592065</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>9090</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -2768,32 +2844,32 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.3244</v>
+        <v>0.4964</v>
       </c>
       <c r="H20" t="n">
-        <v>31.18</v>
+        <v>35.93</v>
       </c>
       <c r="I20" t="n">
-        <v>37.73</v>
+        <v>43.25</v>
       </c>
       <c r="J20" t="n">
-        <v>-26.21</v>
+        <v>-28.06</v>
       </c>
       <c r="K20" t="n">
-        <v>0.008069549282663851</v>
+        <v>0.009043569810587505</v>
       </c>
       <c r="L20" t="n">
-        <v>0.475712653229118</v>
+        <v>0.4697706118710646</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.071290395139989</v>
+        <v>-3.444027144930838</v>
       </c>
       <c r="N20" t="n">
-        <v>-30.23264965681447</v>
+        <v>-30.88404811946089</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -2856,12 +2932,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>3N-9090</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -2871,14 +2947,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>592156</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D21" t="n">
-        <v>9080</v>
+          <t>592180</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>9080</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -2891,28 +2971,28 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.4763</v>
+        <v>0.5157</v>
       </c>
       <c r="H21" t="n">
-        <v>31.1</v>
+        <v>31.12</v>
       </c>
       <c r="I21" t="n">
-        <v>42.23</v>
+        <v>42.89</v>
       </c>
       <c r="J21" t="n">
-        <v>-28.14</v>
+        <v>-28.34</v>
       </c>
       <c r="K21" t="n">
-        <v>0.007640021982123706</v>
+        <v>0.008368364062059925</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4713123370477795</v>
+        <v>0.4654813415219559</v>
       </c>
       <c r="M21" t="n">
-        <v>-5.275231149573679</v>
+        <v>-3.858830262004631</v>
       </c>
       <c r="N21" t="n">
-        <v>-31.14655197754229</v>
+        <v>-31.39933347050956</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2975,12 +3055,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>8P-9080</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -2990,14 +3070,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>592293</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>14</v>
-      </c>
-      <c r="D22" t="n">
-        <v>580</v>
+          <t>592225</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -3006,32 +3090,32 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.4944</v>
+        <v>0.3244</v>
       </c>
       <c r="H22" t="n">
-        <v>31.52</v>
+        <v>31.18</v>
       </c>
       <c r="I22" t="n">
-        <v>42.3</v>
+        <v>37.73</v>
       </c>
       <c r="J22" t="n">
-        <v>-26.48</v>
+        <v>-26.21</v>
       </c>
       <c r="K22" t="n">
-        <v>0.01076601867180658</v>
+        <v>0.008069549282663851</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4577242403784301</v>
+        <v>0.475712653229118</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.046262785260377</v>
+        <v>-4.071290395139989</v>
       </c>
       <c r="N22" t="n">
-        <v>-29.99931289407546</v>
+        <v>-30.23264965681447</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -3094,12 +3178,12 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>11P-580</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -3109,48 +3193,52 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>592141</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>7</v>
-      </c>
-      <c r="D23" t="n">
-        <v>378</v>
+          <t>592156</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Alchornea lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.4645</v>
+        <v>0.4763</v>
       </c>
       <c r="H23" t="n">
-        <v>28.5</v>
+        <v>31.1</v>
       </c>
       <c r="I23" t="n">
-        <v>45.94</v>
+        <v>42.23</v>
       </c>
       <c r="J23" t="n">
-        <v>-26</v>
+        <v>-28.14</v>
       </c>
       <c r="K23" t="n">
-        <v>0.01132472571893583</v>
+        <v>0.007640021982123706</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4942085040254546</v>
+        <v>0.4713123370477795</v>
       </c>
       <c r="M23" t="n">
-        <v>-6.641046291158119</v>
+        <v>-5.275231149573679</v>
       </c>
       <c r="N23" t="n">
-        <v>-28.62845941298373</v>
+        <v>-31.14655197754229</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -3213,12 +3301,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>8P-378</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -3228,14 +3316,18 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>592087</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>3</v>
-      </c>
-      <c r="D24" t="n">
-        <v>9738</v>
+          <t>592293</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>9738</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -3244,32 +3336,32 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.2875</v>
+        <v>0.4944</v>
       </c>
       <c r="H24" t="n">
-        <v>29.93</v>
+        <v>31.52</v>
       </c>
       <c r="I24" t="n">
-        <v>37.55</v>
+        <v>42.3</v>
       </c>
       <c r="J24" t="n">
-        <v>-28.88</v>
+        <v>-26.48</v>
       </c>
       <c r="K24" t="n">
-        <v>0.009576658357029219</v>
+        <v>0.01076601867180658</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4622755786308759</v>
+        <v>0.4577242403784301</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.290672136481755</v>
+        <v>-1.046262785260377</v>
       </c>
       <c r="N24" t="n">
-        <v>-32.34240288657975</v>
+        <v>-29.99931289407546</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -3332,12 +3424,12 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>14NP-9738</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -3347,48 +3439,52 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>592041</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" t="n">
-        <v>356</v>
+          <t>592141</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Myrcia sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.52</v>
+        <v>0.4645</v>
       </c>
       <c r="H25" t="n">
-        <v>29.34</v>
+        <v>28.5</v>
       </c>
       <c r="I25" t="n">
-        <v>42.75</v>
+        <v>45.94</v>
       </c>
       <c r="J25" t="n">
-        <v>-27.5</v>
+        <v>-26</v>
       </c>
       <c r="K25" t="n">
-        <v>0.008624197851075254</v>
+        <v>0.01132472571893583</v>
       </c>
       <c r="L25" t="n">
-        <v>0.480241325154702</v>
+        <v>0.4942085040254546</v>
       </c>
       <c r="M25" t="n">
-        <v>-4.202813334699972</v>
+        <v>-6.641046291158119</v>
       </c>
       <c r="N25" t="n">
-        <v>-30.70904554740663</v>
+        <v>-28.62845941298373</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -3451,12 +3547,12 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>7C-356</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -3466,48 +3562,52 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>592043</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" t="n">
-        <v>172</v>
+          <t>592087</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alchornea lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.4715</v>
+        <v>0.2875</v>
       </c>
       <c r="H26" t="n">
-        <v>30.2</v>
+        <v>29.93</v>
       </c>
       <c r="I26" t="n">
-        <v>45.23</v>
+        <v>37.55</v>
       </c>
       <c r="J26" t="n">
-        <v>-26.24</v>
+        <v>-28.88</v>
       </c>
       <c r="K26" t="n">
-        <v>0.01046889599080897</v>
+        <v>0.009576658357029219</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4873570429631284</v>
+        <v>0.4622755786308759</v>
       </c>
       <c r="M26" t="n">
-        <v>-5.254996851179836</v>
+        <v>-2.290672136481755</v>
       </c>
       <c r="N26" t="n">
-        <v>-28.97846455709225</v>
+        <v>-32.34240288657975</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -3570,12 +3670,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>3N-172</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -3585,48 +3685,52 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>592064</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>3</v>
-      </c>
-      <c r="D27" t="n">
-        <v>9084</v>
+          <t>592041</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>9084</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Alchornea lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.2302</v>
+        <v>0.52</v>
       </c>
       <c r="H27" t="n">
-        <v>30.5</v>
+        <v>29.34</v>
       </c>
       <c r="I27" t="n">
-        <v>39.56</v>
+        <v>42.75</v>
       </c>
       <c r="J27" t="n">
-        <v>-25.06</v>
+        <v>-27.5</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0167144923455957</v>
+        <v>0.008624197851075254</v>
       </c>
       <c r="L27" t="n">
-        <v>0.4810907835092114</v>
+        <v>0.480241325154702</v>
       </c>
       <c r="M27" t="n">
-        <v>-4.083030602171767</v>
+        <v>-4.202813334699972</v>
       </c>
       <c r="N27" t="n">
-        <v>-28.09576659038901</v>
+        <v>-30.70904554740663</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -3689,12 +3793,12 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>2P-9084</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -3704,14 +3808,18 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>592046</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>2</v>
-      </c>
-      <c r="D28" t="n">
-        <v>254</v>
+          <t>592043</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -3724,28 +3832,28 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.4745</v>
+        <v>0.4715</v>
       </c>
       <c r="H28" t="n">
-        <v>27.91</v>
+        <v>30.2</v>
       </c>
       <c r="I28" t="n">
-        <v>46.97</v>
+        <v>45.23</v>
       </c>
       <c r="J28" t="n">
-        <v>-29.12</v>
+        <v>-26.24</v>
       </c>
       <c r="K28" t="n">
-        <v>0.01195308081094234</v>
+        <v>0.01046889599080897</v>
       </c>
       <c r="L28" t="n">
-        <v>0.481242508831294</v>
+        <v>0.4873570429631284</v>
       </c>
       <c r="M28" t="n">
-        <v>-4.790631786771964</v>
+        <v>-5.254996851179836</v>
       </c>
       <c r="N28" t="n">
-        <v>-30.63019832189168</v>
+        <v>-28.97846455709225</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -3808,12 +3916,12 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>2P-254</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -3823,14 +3931,18 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>592046</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>2</v>
-      </c>
-      <c r="D29" t="n">
-        <v>8396</v>
+          <t>592064</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>8396</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -3839,32 +3951,32 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.4465</v>
+        <v>0.2302</v>
       </c>
       <c r="H29" t="n">
-        <v>28.45</v>
+        <v>30.5</v>
       </c>
       <c r="I29" t="n">
-        <v>46.97</v>
+        <v>39.56</v>
       </c>
       <c r="J29" t="n">
-        <v>-29.12</v>
+        <v>-25.06</v>
       </c>
       <c r="K29" t="n">
-        <v>0.01195308081094234</v>
+        <v>0.0167144923455957</v>
       </c>
       <c r="L29" t="n">
-        <v>0.481242508831294</v>
+        <v>0.4810907835092114</v>
       </c>
       <c r="M29" t="n">
-        <v>-4.790631786771964</v>
+        <v>-4.083030602171767</v>
       </c>
       <c r="N29" t="n">
-        <v>-30.63019832189168</v>
+        <v>-28.09576659038901</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -3927,12 +4039,12 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>3N-8396</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -3942,14 +4054,18 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>592004</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="n">
-        <v>7924</v>
+          <t>592046</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>7924</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -3958,32 +4074,32 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.4311</v>
+        <v>0.4745</v>
       </c>
       <c r="H30" t="n">
-        <v>28.02</v>
+        <v>27.91</v>
       </c>
       <c r="I30" t="n">
-        <v>43.95</v>
+        <v>46.97</v>
       </c>
       <c r="J30" t="n">
-        <v>-28</v>
+        <v>-29.12</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01277139289547326</v>
+        <v>0.01195308081094234</v>
       </c>
       <c r="L30" t="n">
-        <v>0.4933372659575072</v>
+        <v>0.481242508831294</v>
       </c>
       <c r="M30" t="n">
-        <v>-4.840193734106043</v>
+        <v>-4.790631786771964</v>
       </c>
       <c r="N30" t="n">
-        <v>-29.75625376622231</v>
+        <v>-30.63019832189168</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -4046,12 +4162,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>2P-7924</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -4061,14 +4177,18 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>592037</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>2</v>
-      </c>
-      <c r="D31" t="n">
-        <v>7924</v>
+          <t>592046</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>7924</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -4081,28 +4201,28 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.2546</v>
+        <v>0.4465</v>
       </c>
       <c r="H31" t="n">
-        <v>28.36</v>
+        <v>28.45</v>
       </c>
       <c r="I31" t="n">
-        <v>46.17</v>
+        <v>46.97</v>
       </c>
       <c r="J31" t="n">
-        <v>-26.15</v>
+        <v>-29.12</v>
       </c>
       <c r="K31" t="n">
-        <v>0.01022929018745756</v>
+        <v>0.01195308081094234</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4869595854031584</v>
+        <v>0.481242508831294</v>
       </c>
       <c r="M31" t="n">
-        <v>-5.406754089133663</v>
+        <v>-4.790631786771964</v>
       </c>
       <c r="N31" t="n">
-        <v>-28.59929231764135</v>
+        <v>-30.63019832189168</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -4165,12 +4285,12 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>2P-7924</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -4180,14 +4300,18 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>592037</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>2</v>
-      </c>
-      <c r="D32" t="n">
-        <v>69</v>
+          <t>592004</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -4196,32 +4320,32 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.4824</v>
+        <v>0.4311</v>
       </c>
       <c r="H32" t="n">
-        <v>27.41</v>
+        <v>28.02</v>
       </c>
       <c r="I32" t="n">
-        <v>46.17</v>
+        <v>43.95</v>
       </c>
       <c r="J32" t="n">
-        <v>-26.15</v>
+        <v>-28</v>
       </c>
       <c r="K32" t="n">
-        <v>0.01022929018745756</v>
+        <v>0.01277139289547326</v>
       </c>
       <c r="L32" t="n">
-        <v>0.4869595854031584</v>
+        <v>0.4933372659575072</v>
       </c>
       <c r="M32" t="n">
-        <v>-5.406754089133663</v>
+        <v>-4.840193734106043</v>
       </c>
       <c r="N32" t="n">
-        <v>-28.59929231764135</v>
+        <v>-29.75625376622231</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -4284,12 +4408,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>1C-69</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -4299,14 +4423,18 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>592073</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>3</v>
-      </c>
-      <c r="D33" t="n">
-        <v>7922</v>
+          <t>592037</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>7922</t>
+        </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -4315,32 +4443,32 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.4821</v>
+        <v>0.2546</v>
       </c>
       <c r="H33" t="n">
-        <v>30.59</v>
+        <v>28.36</v>
       </c>
       <c r="I33" t="n">
-        <v>44.41</v>
+        <v>46.17</v>
       </c>
       <c r="J33" t="n">
-        <v>-26.21</v>
+        <v>-26.15</v>
       </c>
       <c r="K33" t="n">
-        <v>0.01248762912504004</v>
+        <v>0.01022929018745756</v>
       </c>
       <c r="L33" t="n">
-        <v>0.4757300739618544</v>
+        <v>0.4869595854031584</v>
       </c>
       <c r="M33" t="n">
-        <v>-3.120278370629341</v>
+        <v>-5.406754089133663</v>
       </c>
       <c r="N33" t="n">
-        <v>-28.73540542923911</v>
+        <v>-28.59929231764135</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -4403,12 +4531,12 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>2P-7922</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -4418,14 +4546,18 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>592227</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>11</v>
-      </c>
-      <c r="D34" t="n">
-        <v>7922</v>
+          <t>592037</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>7922</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -4438,28 +4570,28 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.4471</v>
+        <v>0.4824</v>
       </c>
       <c r="H34" t="n">
-        <v>30.07</v>
+        <v>27.41</v>
       </c>
       <c r="I34" t="n">
-        <v>47.48</v>
+        <v>46.17</v>
       </c>
       <c r="J34" t="n">
-        <v>-26</v>
+        <v>-26.15</v>
       </c>
       <c r="K34" t="n">
-        <v>0.01346916593366116</v>
+        <v>0.01022929018745756</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4828651621894796</v>
+        <v>0.4869595854031584</v>
       </c>
       <c r="M34" t="n">
-        <v>-4.567030705789156</v>
+        <v>-5.406754089133663</v>
       </c>
       <c r="N34" t="n">
-        <v>-28.14234115727744</v>
+        <v>-28.59929231764135</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -4522,12 +4654,12 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>2P-7922</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -4537,14 +4669,18 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>592223</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>11</v>
-      </c>
-      <c r="D35" t="n">
-        <v>141</v>
+          <t>592073</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -4553,32 +4689,32 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.4747</v>
+        <v>0.4821</v>
       </c>
       <c r="H35" t="n">
-        <v>32.21</v>
+        <v>30.59</v>
       </c>
       <c r="I35" t="n">
-        <v>45.05</v>
+        <v>44.41</v>
       </c>
       <c r="J35" t="n">
-        <v>-25.9</v>
+        <v>-26.21</v>
       </c>
       <c r="K35" t="n">
-        <v>0.01039231601447498</v>
+        <v>0.01248762912504004</v>
       </c>
       <c r="L35" t="n">
-        <v>0.4872522150414987</v>
+        <v>0.4757300739618544</v>
       </c>
       <c r="M35" t="n">
-        <v>-4.071290395139989</v>
+        <v>-3.120278370629341</v>
       </c>
       <c r="N35" t="n">
-        <v>-29.11457766869001</v>
+        <v>-28.73540542923911</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -4641,12 +4777,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>3N-141</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -4656,14 +4792,18 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>592231</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>11</v>
-      </c>
-      <c r="D36" t="n">
-        <v>587</v>
+          <t>592227</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -4676,28 +4816,28 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.4813</v>
+        <v>0.4471</v>
       </c>
       <c r="H36" t="n">
-        <v>29.05</v>
+        <v>30.07</v>
       </c>
       <c r="I36" t="n">
-        <v>44.19</v>
+        <v>47.48</v>
       </c>
       <c r="J36" t="n">
-        <v>-28.04</v>
+        <v>-26</v>
       </c>
       <c r="K36" t="n">
-        <v>0.00947542112608599</v>
+        <v>0.01346916593366116</v>
       </c>
       <c r="L36" t="n">
-        <v>0.4852181812280615</v>
+        <v>0.4828651621894796</v>
       </c>
       <c r="M36" t="n">
-        <v>-3.899298858792318</v>
+        <v>-4.567030705789156</v>
       </c>
       <c r="N36" t="n">
-        <v>-29.86319978247769</v>
+        <v>-28.14234115727744</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -4760,12 +4900,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>11P-587</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -4775,14 +4915,18 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>592273</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>13</v>
-      </c>
-      <c r="D37" t="n">
-        <v>575</v>
+          <t>592223</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -4791,32 +4935,32 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.4925</v>
+        <v>0.4747</v>
       </c>
       <c r="H37" t="n">
-        <v>28.39</v>
+        <v>32.21</v>
       </c>
       <c r="I37" t="n">
-        <v>42.25</v>
+        <v>45.05</v>
       </c>
       <c r="J37" t="n">
-        <v>-26.86</v>
+        <v>-25.9</v>
       </c>
       <c r="K37" t="n">
-        <v>0.01107357019166795</v>
+        <v>0.01039231601447498</v>
       </c>
       <c r="L37" t="n">
-        <v>0.4956113551604984</v>
+        <v>0.4872522150414987</v>
       </c>
       <c r="M37" t="n">
-        <v>-4.02070464915538</v>
+        <v>-4.071290395139989</v>
       </c>
       <c r="N37" t="n">
-        <v>-29.61041828951042</v>
+        <v>-29.11457766869001</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -4879,12 +5023,12 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>11P-575</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -4894,14 +5038,18 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>592269</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>13</v>
-      </c>
-      <c r="D38" t="n">
-        <v>596</v>
+          <t>592231</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -4910,32 +5058,32 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.4714</v>
+        <v>0.4813</v>
       </c>
       <c r="H38" t="n">
-        <v>27.94</v>
+        <v>29.05</v>
       </c>
       <c r="I38" t="n">
-        <v>44.05</v>
+        <v>44.19</v>
       </c>
       <c r="J38" t="n">
-        <v>-27.9</v>
+        <v>-28.04</v>
       </c>
       <c r="K38" t="n">
-        <v>0.01261612726319458</v>
+        <v>0.00947542112608599</v>
       </c>
       <c r="L38" t="n">
-        <v>0.4855407560072135</v>
+        <v>0.4852181812280615</v>
       </c>
       <c r="M38" t="n">
-        <v>-3.403558548143151</v>
+        <v>-3.899298858792318</v>
       </c>
       <c r="N38" t="n">
-        <v>-29.91181160804832</v>
+        <v>-29.86319978247769</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -4998,12 +5146,12 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>11P-596</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -5013,14 +5161,18 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>592299</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>14</v>
-      </c>
-      <c r="D39" t="n">
-        <v>631</v>
+          <t>592273</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -5029,32 +5181,32 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.4764</v>
+        <v>0.4925</v>
       </c>
       <c r="H39" t="n">
-        <v>30.31</v>
+        <v>28.39</v>
       </c>
       <c r="I39" t="n">
-        <v>45.36</v>
+        <v>42.25</v>
       </c>
       <c r="J39" t="n">
-        <v>-25.93</v>
+        <v>-26.86</v>
       </c>
       <c r="K39" t="n">
-        <v>0.01270327966515974</v>
+        <v>0.01107357019166795</v>
       </c>
       <c r="L39" t="n">
-        <v>0.4830906453161209</v>
+        <v>0.4956113551604984</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.511651648318779</v>
+        <v>-4.02070464915538</v>
       </c>
       <c r="N39" t="n">
-        <v>-29.20207895471714</v>
+        <v>-29.61041828951042</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -5117,12 +5269,12 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>13N-631</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -5132,14 +5284,18 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>592105</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>4</v>
-      </c>
-      <c r="D40" t="n">
-        <v>4445</v>
+          <t>592269</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4445</t>
+        </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -5148,32 +5304,32 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.4891</v>
+        <v>0.4714</v>
       </c>
       <c r="H40" t="n">
-        <v>29.73</v>
+        <v>27.94</v>
       </c>
       <c r="I40" t="n">
-        <v>45.33</v>
+        <v>44.05</v>
       </c>
       <c r="J40" t="n">
-        <v>-24.8</v>
+        <v>-27.9</v>
       </c>
       <c r="K40" t="n">
-        <v>0.01143301724974359</v>
+        <v>0.01261612726319458</v>
       </c>
       <c r="L40" t="n">
-        <v>0.4880939859568743</v>
+        <v>0.4855407560072135</v>
       </c>
       <c r="M40" t="n">
-        <v>-3.029224027857045</v>
+        <v>-3.403558548143151</v>
       </c>
       <c r="N40" t="n">
-        <v>-27.42288613883214</v>
+        <v>-29.91181160804832</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -5236,12 +5392,12 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>13N-4445</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -5251,14 +5407,18 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>592220</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>11</v>
-      </c>
-      <c r="D41" t="n">
-        <v>6976</v>
+          <t>592299</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>6976</t>
+        </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -5267,32 +5427,32 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.4646</v>
+        <v>0.4764</v>
       </c>
       <c r="H41" t="n">
-        <v>29.27</v>
+        <v>30.31</v>
       </c>
       <c r="I41" t="n">
-        <v>45.34</v>
+        <v>45.36</v>
       </c>
       <c r="J41" t="n">
-        <v>-26.05</v>
+        <v>-25.93</v>
       </c>
       <c r="K41" t="n">
-        <v>0.01146485586470221</v>
+        <v>0.01270327966515974</v>
       </c>
       <c r="L41" t="n">
-        <v>0.4921234286150691</v>
+        <v>0.4830906453161209</v>
       </c>
       <c r="M41" t="n">
-        <v>-5.103239613226009</v>
+        <v>-1.511651648318779</v>
       </c>
       <c r="N41" t="n">
-        <v>-28.37567792001646</v>
+        <v>-29.20207895471714</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -5355,12 +5515,12 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>14NP-6976</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -5370,14 +5530,18 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>592198</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>9</v>
-      </c>
-      <c r="D42" t="n">
-        <v>213</v>
+          <t>592105</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -5390,28 +5554,28 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.4834</v>
+        <v>0.4891</v>
       </c>
       <c r="H42" t="n">
-        <v>29.57</v>
+        <v>29.73</v>
       </c>
       <c r="I42" t="n">
-        <v>44.21</v>
+        <v>45.33</v>
       </c>
       <c r="J42" t="n">
-        <v>-28.37</v>
+        <v>-24.8</v>
       </c>
       <c r="K42" t="n">
-        <v>0.01037404380149425</v>
+        <v>0.01143301724974359</v>
       </c>
       <c r="L42" t="n">
-        <v>0.4166713847134191</v>
+        <v>0.4880939859568743</v>
       </c>
       <c r="M42" t="n">
-        <v>-2.219852092103304</v>
+        <v>-3.029224027857045</v>
       </c>
       <c r="N42" t="n">
-        <v>-31.19516380311292</v>
+        <v>-27.42288613883214</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -5474,12 +5638,12 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>4NP-213</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -5489,48 +5653,52 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>592092</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>4</v>
-      </c>
-      <c r="D43" t="n">
-        <v>569</v>
+          <t>592220</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Myrcia sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.1608</v>
+        <v>0.4646</v>
       </c>
       <c r="H43" t="n">
-        <v>32.03</v>
+        <v>29.27</v>
       </c>
       <c r="I43" t="n">
-        <v>27.72</v>
+        <v>45.34</v>
       </c>
       <c r="J43" t="n">
-        <v>-25.93</v>
+        <v>-26.05</v>
       </c>
       <c r="K43" t="n">
-        <v>0.008560510087377649</v>
+        <v>0.01146485586470221</v>
       </c>
       <c r="L43" t="n">
-        <v>0.4635134600090949</v>
+        <v>0.4921234286150691</v>
       </c>
       <c r="M43" t="n">
-        <v>-1.57235454350031</v>
+        <v>-5.103239613226009</v>
       </c>
       <c r="N43" t="n">
-        <v>-29.27013551051603</v>
+        <v>-28.37567792001646</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -5593,12 +5761,12 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>11P-569</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -5608,18 +5776,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>592092</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>4</v>
-      </c>
-      <c r="D44" t="n">
-        <v>8361</v>
+          <t>592198</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>8361</t>
+        </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Myrcia sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5628,28 +5800,28 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.1608</v>
+        <v>0.4834</v>
       </c>
       <c r="H44" t="n">
-        <v>32.03</v>
+        <v>29.57</v>
       </c>
       <c r="I44" t="n">
-        <v>13.17</v>
+        <v>44.21</v>
       </c>
       <c r="J44" t="n">
-        <v>-25.82</v>
+        <v>-28.37</v>
       </c>
       <c r="K44" t="n">
-        <v>0.008560510087377649</v>
+        <v>0.01037404380149425</v>
       </c>
       <c r="L44" t="n">
-        <v>0.4635134600090949</v>
+        <v>0.4166713847134191</v>
       </c>
       <c r="M44" t="n">
-        <v>-1.57235454350031</v>
+        <v>-2.219852092103304</v>
       </c>
       <c r="N44" t="n">
-        <v>-29.27013551051603</v>
+        <v>-31.19516380311292</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -5712,12 +5884,12 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>9NP-8361</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -5727,18 +5899,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>592206</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>9</v>
-      </c>
-      <c r="D45" t="n">
-        <v>191</v>
+          <t>592092</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Alchornea lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5747,28 +5923,28 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.4705</v>
+        <v>0.1608</v>
       </c>
       <c r="H45" t="n">
-        <v>30.14</v>
+        <v>32.03</v>
       </c>
       <c r="I45" t="n">
-        <v>44.47</v>
+        <v>27.72</v>
       </c>
       <c r="J45" t="n">
-        <v>-28.43</v>
+        <v>-25.93</v>
       </c>
       <c r="K45" t="n">
-        <v>0.01420329104490789</v>
+        <v>0.008560510087377649</v>
       </c>
       <c r="L45" t="n">
-        <v>0.4918643195929212</v>
+        <v>0.4635134600090949</v>
       </c>
       <c r="M45" t="n">
-        <v>-1.896103317801807</v>
+        <v>-1.57235454350031</v>
       </c>
       <c r="N45" t="n">
-        <v>-30.81599156366202</v>
+        <v>-29.27013551051603</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -5831,12 +6007,12 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>4NP-191</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -5846,48 +6022,52 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>592249</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>12</v>
-      </c>
-      <c r="D46" t="n">
-        <v>191</v>
+          <t>592092</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Alchornea lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.4734</v>
+        <v>0.1608</v>
       </c>
       <c r="H46" t="n">
-        <v>28.99</v>
+        <v>32.03</v>
       </c>
       <c r="I46" t="n">
-        <v>46.15</v>
+        <v>13.17</v>
       </c>
       <c r="J46" t="n">
-        <v>-26.23</v>
+        <v>-25.82</v>
       </c>
       <c r="K46" t="n">
-        <v>0.01099101588878326</v>
+        <v>0.008560510087377649</v>
       </c>
       <c r="L46" t="n">
-        <v>0.4934962766238894</v>
+        <v>0.4635134600090949</v>
       </c>
       <c r="M46" t="n">
-        <v>-4.526562109001468</v>
+        <v>-1.57235454350031</v>
       </c>
       <c r="N46" t="n">
-        <v>-28.92985273152162</v>
+        <v>-29.27013551051603</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -5950,12 +6130,12 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>4NP-191</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -5965,14 +6145,18 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>592162</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>8</v>
-      </c>
-      <c r="D47" t="n">
-        <v>4469</v>
+          <t>592206</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>4469</t>
+        </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -5981,32 +6165,32 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.43</v>
+        <v>0.4705</v>
       </c>
       <c r="H47" t="n">
-        <v>29.56</v>
+        <v>30.14</v>
       </c>
       <c r="I47" t="n">
-        <v>46.4</v>
+        <v>44.47</v>
       </c>
       <c r="J47" t="n">
-        <v>-27.36</v>
+        <v>-28.43</v>
       </c>
       <c r="K47" t="n">
-        <v>0.01126937079351205</v>
+        <v>0.01420329104490789</v>
       </c>
       <c r="L47" t="n">
-        <v>0.4951107797338253</v>
+        <v>0.4918643195929212</v>
       </c>
       <c r="M47" t="n">
-        <v>-5.629331371465942</v>
+        <v>-1.896103317801807</v>
       </c>
       <c r="N47" t="n">
-        <v>-29.85347741736357</v>
+        <v>-30.81599156366202</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -6069,12 +6253,12 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>9NP-4469</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -6084,48 +6268,52 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>592317</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>16</v>
-      </c>
-      <c r="D48" t="n">
-        <v>4894</v>
+          <t>592249</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>4894</t>
+        </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Myrcia sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.4983</v>
+        <v>0.4734</v>
       </c>
       <c r="H48" t="n">
-        <v>31.17</v>
+        <v>28.99</v>
       </c>
       <c r="I48" t="n">
-        <v>42.88</v>
+        <v>46.15</v>
       </c>
       <c r="J48" t="n">
-        <v>-27.21</v>
+        <v>-26.23</v>
       </c>
       <c r="K48" t="n">
-        <v>0.007344029105360788</v>
+        <v>0.01099101588878326</v>
       </c>
       <c r="L48" t="n">
-        <v>0.4607625303936961</v>
+        <v>0.4934962766238894</v>
       </c>
       <c r="M48" t="n">
-        <v>-5.700151415844394</v>
+        <v>-4.526562109001468</v>
       </c>
       <c r="N48" t="n">
-        <v>-30.94238231014565</v>
+        <v>-28.92985273152162</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -6188,12 +6376,12 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>12C-4894</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -6203,14 +6391,18 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>592323</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>16</v>
-      </c>
-      <c r="D49" t="n">
-        <v>389</v>
+          <t>592162</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -6223,28 +6415,28 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.4509</v>
+        <v>0.43</v>
       </c>
       <c r="H49" t="n">
-        <v>32.94</v>
+        <v>29.56</v>
       </c>
       <c r="I49" t="n">
-        <v>42.07</v>
+        <v>46.4</v>
       </c>
       <c r="J49" t="n">
-        <v>-26.72</v>
+        <v>-27.36</v>
       </c>
       <c r="K49" t="n">
-        <v>0.008096701323966792</v>
+        <v>0.01126937079351205</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4601026255576515</v>
+        <v>0.4951107797338253</v>
       </c>
       <c r="M49" t="n">
-        <v>-6.064368786933578</v>
+        <v>-5.629331371465942</v>
       </c>
       <c r="N49" t="n">
-        <v>-30.55348770558062</v>
+        <v>-29.85347741736357</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -6307,12 +6499,12 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>8P-389</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -6322,14 +6514,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>592325</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>16</v>
-      </c>
-      <c r="D50" t="n">
-        <v>746</v>
+          <t>592317</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -6342,28 +6538,28 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.4628</v>
+        <v>0.4983</v>
       </c>
       <c r="H50" t="n">
-        <v>28.81</v>
+        <v>31.17</v>
       </c>
       <c r="I50" t="n">
-        <v>42.69</v>
+        <v>42.88</v>
       </c>
       <c r="J50" t="n">
-        <v>-26.48</v>
+        <v>-27.21</v>
       </c>
       <c r="K50" t="n">
-        <v>0.009380420574156176</v>
+        <v>0.007344029105360788</v>
       </c>
       <c r="L50" t="n">
-        <v>0.4875151335935864</v>
+        <v>0.4607625303936961</v>
       </c>
       <c r="M50" t="n">
-        <v>-3.939767455580006</v>
+        <v>-5.700151415844394</v>
       </c>
       <c r="N50" t="n">
-        <v>-29.71736430576581</v>
+        <v>-30.94238231014565</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -6426,12 +6622,12 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>16P-746</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -6441,14 +6637,18 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>592365</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>18</v>
-      </c>
-      <c r="D51" t="n">
-        <v>763</v>
+          <t>592323</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -6457,32 +6657,32 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.463</v>
+        <v>0.4509</v>
       </c>
       <c r="H51" t="n">
-        <v>28.11</v>
+        <v>32.94</v>
       </c>
       <c r="I51" t="n">
-        <v>45.52</v>
+        <v>42.07</v>
       </c>
       <c r="J51" t="n">
-        <v>-27.66</v>
+        <v>-26.72</v>
       </c>
       <c r="K51" t="n">
-        <v>0.01443808885426148</v>
+        <v>0.008096701323966792</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5011863992799793</v>
+        <v>0.4601026255576515</v>
       </c>
       <c r="M51" t="n">
-        <v>-1.724111781454136</v>
+        <v>-6.064368786933578</v>
       </c>
       <c r="N51" t="n">
-        <v>-31.04932832640103</v>
+        <v>-30.55348770558062</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -6545,12 +6745,12 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>16P-763</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -6560,14 +6760,18 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>592344</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>17</v>
-      </c>
-      <c r="D52" t="n">
-        <v>768</v>
+          <t>592325</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -6576,32 +6780,32 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.5123</v>
+        <v>0.4628</v>
       </c>
       <c r="H52" t="n">
-        <v>30.15</v>
+        <v>28.81</v>
       </c>
       <c r="I52" t="n">
-        <v>41.93</v>
+        <v>42.69</v>
       </c>
       <c r="J52" t="n">
-        <v>-26.16</v>
+        <v>-26.48</v>
       </c>
       <c r="K52" t="n">
-        <v>0.02957614146330922</v>
+        <v>0.009380420574156176</v>
       </c>
       <c r="L52" t="n">
-        <v>0.4977600594607596</v>
+        <v>0.4875151335935864</v>
       </c>
       <c r="M52" t="n">
-        <v>2.373333643299183</v>
+        <v>-3.939767455580006</v>
       </c>
       <c r="N52" t="n">
-        <v>-30.32987330795573</v>
+        <v>-29.71736430576581</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -6664,12 +6868,12 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>16P-768</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -6679,18 +6883,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>592359</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>18</v>
-      </c>
-      <c r="D53" t="n">
-        <v>4940</v>
+          <t>592365</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>4940</t>
+        </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Myrcia sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6699,28 +6907,28 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.5259</v>
+        <v>0.463</v>
       </c>
       <c r="H53" t="n">
-        <v>29.2</v>
+        <v>28.11</v>
       </c>
       <c r="I53" t="n">
-        <v>42.31</v>
+        <v>45.52</v>
       </c>
       <c r="J53" t="n">
-        <v>-28.6</v>
+        <v>-27.66</v>
       </c>
       <c r="K53" t="n">
-        <v>0.009600430650899688</v>
+        <v>0.01443808885426148</v>
       </c>
       <c r="L53" t="n">
-        <v>0.4691406472935918</v>
+        <v>0.5011863992799793</v>
       </c>
       <c r="M53" t="n">
-        <v>-2.250203539694068</v>
+        <v>-1.724111781454136</v>
       </c>
       <c r="N53" t="n">
-        <v>-31.96323064712885</v>
+        <v>-31.04932832640103</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -6783,12 +6991,12 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>18NP-4940</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -6798,14 +7006,18 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>592246</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>12</v>
-      </c>
-      <c r="D54" t="n">
-        <v>902</v>
+          <t>592344</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -6818,28 +7030,28 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.5074</v>
+        <v>0.5123</v>
       </c>
       <c r="H54" t="n">
-        <v>31.59</v>
+        <v>30.15</v>
       </c>
       <c r="I54" t="n">
-        <v>42.4</v>
+        <v>41.93</v>
       </c>
       <c r="J54" t="n">
-        <v>-27.66</v>
+        <v>-26.16</v>
       </c>
       <c r="K54" t="n">
-        <v>0.009823049740848884</v>
+        <v>0.02957614146330922</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4763186584092498</v>
+        <v>0.4977600594607596</v>
       </c>
       <c r="M54" t="n">
-        <v>-2.71559240275247</v>
+        <v>2.373333643299183</v>
       </c>
       <c r="N54" t="n">
-        <v>-31.27294272402593</v>
+        <v>-30.32987330795573</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -6902,12 +7114,12 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>17C-902</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -6917,14 +7129,18 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>592005</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" t="n">
-        <v>5880</v>
+          <t>592359</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>5880</t>
+        </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -6933,32 +7149,32 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.4941</v>
+        <v>0.5259</v>
       </c>
       <c r="H55" t="n">
-        <v>31.21</v>
+        <v>29.2</v>
       </c>
       <c r="I55" t="n">
-        <v>42.87</v>
+        <v>42.31</v>
       </c>
       <c r="J55" t="n">
-        <v>-26.71</v>
+        <v>-28.6</v>
       </c>
       <c r="K55" t="n">
-        <v>0.009051800629395167</v>
+        <v>0.009600430650899688</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4748134274758074</v>
+        <v>0.4691406472935918</v>
       </c>
       <c r="M55" t="n">
-        <v>-4.324219125063033</v>
+        <v>-2.250203539694068</v>
       </c>
       <c r="N55" t="n">
-        <v>-30.18403783124384</v>
+        <v>-31.96323064712885</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -7021,12 +7237,12 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>18NP-5880</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -7036,14 +7252,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>592132</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>7</v>
-      </c>
-      <c r="D56" t="n">
-        <v>708</v>
+          <t>592246</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -7056,28 +7276,28 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.5098</v>
+        <v>0.5074</v>
       </c>
       <c r="H56" t="n">
-        <v>30.1</v>
+        <v>31.59</v>
       </c>
       <c r="I56" t="n">
-        <v>42.24</v>
+        <v>42.4</v>
       </c>
       <c r="J56" t="n">
-        <v>-27.4</v>
+        <v>-27.66</v>
       </c>
       <c r="K56" t="n">
-        <v>0.009343327965948552</v>
+        <v>0.009823049740848884</v>
       </c>
       <c r="L56" t="n">
-        <v>0.4683037812902506</v>
+        <v>0.4763186584092498</v>
       </c>
       <c r="M56" t="n">
-        <v>-5.072888165635244</v>
+        <v>-2.71559240275247</v>
       </c>
       <c r="N56" t="n">
-        <v>-31.11738488219991</v>
+        <v>-31.27294272402593</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -7140,12 +7360,12 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>12C-708</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -7155,14 +7375,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>592361</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>18</v>
-      </c>
-      <c r="D57" t="n">
-        <v>5812</v>
+          <t>592005</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>5812</t>
+        </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -7171,32 +7395,32 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.4941</v>
       </c>
       <c r="H57" t="n">
-        <v>31.17</v>
+        <v>31.21</v>
       </c>
       <c r="I57" t="n">
-        <v>42.4</v>
+        <v>42.87</v>
       </c>
       <c r="J57" t="n">
-        <v>-26.43</v>
+        <v>-26.71</v>
       </c>
       <c r="K57" t="n">
-        <v>0.009184293993073779</v>
+        <v>0.009051800629395167</v>
       </c>
       <c r="L57" t="n">
-        <v>0.4743601134675379</v>
+        <v>0.4748134274758074</v>
       </c>
       <c r="M57" t="n">
-        <v>-3.464261443324682</v>
+        <v>-4.324219125063033</v>
       </c>
       <c r="N57" t="n">
-        <v>-29.99931289407546</v>
+        <v>-30.18403783124384</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -7259,12 +7483,12 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>1C-5812</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -7274,14 +7498,18 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>592074</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>3</v>
-      </c>
-      <c r="D58" t="n">
-        <v>333</v>
+          <t>592132</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -7290,32 +7518,32 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.5143</v>
+        <v>0.5098</v>
       </c>
       <c r="H58" t="n">
-        <v>30.37</v>
+        <v>30.1</v>
       </c>
       <c r="I58" t="n">
-        <v>42.19</v>
+        <v>42.24</v>
       </c>
       <c r="J58" t="n">
-        <v>-27.43</v>
+        <v>-27.4</v>
       </c>
       <c r="K58" t="n">
-        <v>0.01124023297014281</v>
+        <v>0.009343327965948552</v>
       </c>
       <c r="L58" t="n">
-        <v>0.459115547299592</v>
+        <v>0.4683037812902506</v>
       </c>
       <c r="M58" t="n">
-        <v>-2.735826701146314</v>
+        <v>-5.072888165635244</v>
       </c>
       <c r="N58" t="n">
-        <v>-31.27294272402593</v>
+        <v>-31.11738488219991</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -7378,12 +7606,12 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>7C-333</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -7393,48 +7621,52 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>592334</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>17</v>
-      </c>
-      <c r="D59" t="n">
-        <v>816</v>
+          <t>592361</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>816</t>
+        </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Alchornea lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.4933</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>29.68</v>
+        <v>31.17</v>
       </c>
       <c r="I59" t="n">
-        <v>43.68</v>
+        <v>42.4</v>
       </c>
       <c r="J59" t="n">
-        <v>-26.32</v>
+        <v>-26.43</v>
       </c>
       <c r="K59" t="n">
-        <v>0.01253978620434601</v>
+        <v>0.009184293993073779</v>
       </c>
       <c r="L59" t="n">
-        <v>0.4692340189962593</v>
+        <v>0.4743601134675379</v>
       </c>
       <c r="M59" t="n">
-        <v>-3.828478814413865</v>
+        <v>-3.464261443324682</v>
       </c>
       <c r="N59" t="n">
-        <v>-28.33678845955995</v>
+        <v>-29.99931289407546</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -7497,12 +7729,12 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>18NP-816</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -7512,14 +7744,18 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>592016</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="n">
-        <v>143</v>
+          <t>592074</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -7528,32 +7764,32 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.4669</v>
+        <v>0.5143</v>
       </c>
       <c r="H60" t="n">
-        <v>30.47</v>
+        <v>30.37</v>
       </c>
       <c r="I60" t="n">
-        <v>42.16</v>
+        <v>42.19</v>
       </c>
       <c r="J60" t="n">
-        <v>-30.25</v>
+        <v>-27.43</v>
       </c>
       <c r="K60" t="n">
-        <v>0.01039661954264374</v>
+        <v>0.01124023297014281</v>
       </c>
       <c r="L60" t="n">
-        <v>0.4677017124318122</v>
+        <v>0.459115547299592</v>
       </c>
       <c r="M60" t="n">
-        <v>-3.62613583047543</v>
+        <v>-2.735826701146314</v>
       </c>
       <c r="N60" t="n">
-        <v>-33.28547230264994</v>
+        <v>-31.27294272402593</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -7616,12 +7852,12 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>3N-143</t>
         </is>
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -7631,18 +7867,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>592253</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>12</v>
-      </c>
-      <c r="D61" t="n">
-        <v>4932</v>
+          <t>592334</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>4932</t>
+        </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Myrcia sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7651,28 +7891,28 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.5094</v>
+        <v>0.4933</v>
       </c>
       <c r="H61" t="n">
-        <v>30.94</v>
+        <v>29.68</v>
       </c>
       <c r="I61" t="n">
-        <v>42.21</v>
+        <v>43.68</v>
       </c>
       <c r="J61" t="n">
-        <v>-27.08</v>
+        <v>-26.32</v>
       </c>
       <c r="K61" t="n">
-        <v>0.007561106183874684</v>
+        <v>0.01253978620434601</v>
       </c>
       <c r="L61" t="n">
-        <v>0.4712743651873791</v>
+        <v>0.4692340189962593</v>
       </c>
       <c r="M61" t="n">
-        <v>-3.352972802158542</v>
+        <v>-3.828478814413865</v>
       </c>
       <c r="N61" t="n">
-        <v>-30.78682446831964</v>
+        <v>-28.33678845955995</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -7735,12 +7975,12 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>17C-4932</t>
         </is>
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -7750,14 +7990,18 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>592139</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>7</v>
-      </c>
-      <c r="D62" t="n">
-        <v>96</v>
+          <t>592016</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -7770,28 +8014,28 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.5161</v>
+        <v>0.4669</v>
       </c>
       <c r="H62" t="n">
-        <v>30.03</v>
+        <v>30.47</v>
       </c>
       <c r="I62" t="n">
-        <v>42.67</v>
+        <v>42.16</v>
       </c>
       <c r="J62" t="n">
-        <v>-28.4</v>
+        <v>-30.25</v>
       </c>
       <c r="K62" t="n">
-        <v>0.007367161567282079</v>
+        <v>0.01039661954264374</v>
       </c>
       <c r="L62" t="n">
-        <v>0.4644337061503289</v>
+        <v>0.4677017124318122</v>
       </c>
       <c r="M62" t="n">
-        <v>-5.254996851179836</v>
+        <v>-3.62613583047543</v>
       </c>
       <c r="N62" t="n">
-        <v>-31.37016637516718</v>
+        <v>-33.28547230264994</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -7854,12 +8098,12 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>1C-96</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -7869,14 +8113,18 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>592014</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" t="n">
-        <v>729</v>
+          <t>592253</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -7889,28 +8137,28 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.4771</v>
+        <v>0.5094</v>
       </c>
       <c r="H63" t="n">
-        <v>30.91</v>
+        <v>30.94</v>
       </c>
       <c r="I63" t="n">
-        <v>41.04</v>
+        <v>42.21</v>
       </c>
       <c r="J63" t="n">
-        <v>-27.51</v>
+        <v>-27.08</v>
       </c>
       <c r="K63" t="n">
-        <v>0.00877892593496876</v>
+        <v>0.007561106183874684</v>
       </c>
       <c r="L63" t="n">
-        <v>0.4878157441322304</v>
+        <v>0.4712743651873791</v>
       </c>
       <c r="M63" t="n">
-        <v>-2.169266346118695</v>
+        <v>-3.352972802158542</v>
       </c>
       <c r="N63" t="n">
-        <v>-30.85488102411852</v>
+        <v>-30.78682446831964</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -7973,12 +8221,12 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>12C-729</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -7988,14 +8236,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>592136</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>7</v>
-      </c>
-      <c r="D64" t="n">
-        <v>6992</v>
+          <t>592139</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>6992</t>
+        </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -8008,28 +8260,28 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.5111</v>
+        <v>0.5161</v>
       </c>
       <c r="H64" t="n">
-        <v>30.51</v>
+        <v>30.03</v>
       </c>
       <c r="I64" t="n">
-        <v>40.79</v>
+        <v>42.67</v>
       </c>
       <c r="J64" t="n">
-        <v>-27.9</v>
+        <v>-28.4</v>
       </c>
       <c r="K64" t="n">
-        <v>0.007588418524035746</v>
+        <v>0.007367161567282079</v>
       </c>
       <c r="L64" t="n">
-        <v>0.4682661156327045</v>
+        <v>0.4644337061503289</v>
       </c>
       <c r="M64" t="n">
-        <v>-5.275231149573679</v>
+        <v>-5.254996851179836</v>
       </c>
       <c r="N64" t="n">
-        <v>-31.24377562868355</v>
+        <v>-31.37016637516718</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -8092,12 +8344,12 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>7C-6992</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -8107,14 +8359,18 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>592377</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>19</v>
-      </c>
-      <c r="D65" t="n">
-        <v>90</v>
+          <t>592014</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -8123,32 +8379,32 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.5009</v>
+        <v>0.4771</v>
       </c>
       <c r="H65" t="n">
-        <v>30.54</v>
+        <v>30.91</v>
       </c>
       <c r="I65" t="n">
-        <v>44.07</v>
+        <v>41.04</v>
       </c>
       <c r="J65" t="n">
-        <v>-26.6</v>
+        <v>-27.51</v>
       </c>
       <c r="K65" t="n">
-        <v>0.01010365782050968</v>
+        <v>0.00877892593496876</v>
       </c>
       <c r="L65" t="n">
-        <v>0.4776326264379228</v>
+        <v>0.4878157441322304</v>
       </c>
       <c r="M65" t="n">
-        <v>-2.594186612389409</v>
+        <v>-2.169266346118695</v>
       </c>
       <c r="N65" t="n">
-        <v>-30.47570878466761</v>
+        <v>-30.85488102411852</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -8211,12 +8467,12 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>1C-90-4966</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -8226,14 +8482,18 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>592368</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>18</v>
-      </c>
-      <c r="D66" t="n">
-        <v>341</v>
+          <t>592136</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -8242,32 +8502,32 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.507</v>
+        <v>0.5111</v>
       </c>
       <c r="H66" t="n">
-        <v>29.37</v>
+        <v>30.51</v>
       </c>
       <c r="I66" t="n">
-        <v>43.57</v>
+        <v>40.79</v>
       </c>
       <c r="J66" t="n">
-        <v>-28.59</v>
+        <v>-27.9</v>
       </c>
       <c r="K66" t="n">
-        <v>0.01019293904694541</v>
+        <v>0.007588418524035746</v>
       </c>
       <c r="L66" t="n">
-        <v>0.4749931047140236</v>
+        <v>0.4682661156327045</v>
       </c>
       <c r="M66" t="n">
-        <v>-2.37160933005713</v>
+        <v>-5.275231149573679</v>
       </c>
       <c r="N66" t="n">
-        <v>-32.07017666338423</v>
+        <v>-31.24377562868355</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -8330,12 +8590,12 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>7C-341</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -8345,48 +8605,52 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>592320</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>16</v>
-      </c>
-      <c r="D67" t="n">
-        <v>4952</v>
+          <t>592377</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>4952</t>
+        </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Alchornea lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.4834</v>
+        <v>0.5009</v>
       </c>
       <c r="H67" t="n">
-        <v>30.45</v>
+        <v>30.54</v>
       </c>
       <c r="I67" t="n">
-        <v>44.89</v>
+        <v>44.07</v>
       </c>
       <c r="J67" t="n">
-        <v>-25.02</v>
+        <v>-26.6</v>
       </c>
       <c r="K67" t="n">
-        <v>0.01324104334415568</v>
+        <v>0.01010365782050968</v>
       </c>
       <c r="L67" t="n">
-        <v>0.4819853642097298</v>
+        <v>0.4776326264379228</v>
       </c>
       <c r="M67" t="n">
-        <v>-3.261918459386246</v>
+        <v>-2.594186612389409</v>
       </c>
       <c r="N67" t="n">
-        <v>-27.66594526668528</v>
+        <v>-30.47570878466761</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -8449,12 +8713,12 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>19N-4952</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -8464,14 +8728,18 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>592351</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>17</v>
-      </c>
-      <c r="D68" t="n">
-        <v>7578</v>
+          <t>592368</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>7578</t>
+        </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -8480,32 +8748,32 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.5078</v>
+        <v>0.507</v>
       </c>
       <c r="H68" t="n">
-        <v>30.78</v>
+        <v>29.37</v>
       </c>
       <c r="I68" t="n">
-        <v>43.51</v>
+        <v>43.57</v>
       </c>
       <c r="J68" t="n">
-        <v>-26.51</v>
+        <v>-28.59</v>
       </c>
       <c r="K68" t="n">
-        <v>0.008428783054762122</v>
+        <v>0.01019293904694541</v>
       </c>
       <c r="L68" t="n">
-        <v>0.4687094144720008</v>
+        <v>0.4749931047140236</v>
       </c>
       <c r="M68" t="n">
-        <v>-4.809842286515277</v>
+        <v>-2.37160933005713</v>
       </c>
       <c r="N68" t="n">
-        <v>-30.10625891033084</v>
+        <v>-32.07017666338423</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -8568,12 +8836,12 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>18NP-7578</t>
         </is>
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -8583,14 +8851,18 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>592172</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>8</v>
-      </c>
-      <c r="D69" t="n">
-        <v>755</v>
+          <t>592320</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>755</t>
+        </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -8603,28 +8875,28 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.4875</v>
+        <v>0.4834</v>
       </c>
       <c r="H69" t="n">
-        <v>28.73</v>
+        <v>30.45</v>
       </c>
       <c r="I69" t="n">
-        <v>44.83</v>
+        <v>44.89</v>
       </c>
       <c r="J69" t="n">
-        <v>-29.25</v>
+        <v>-25.02</v>
       </c>
       <c r="K69" t="n">
-        <v>0.01145344039013863</v>
+        <v>0.01324104334415568</v>
       </c>
       <c r="L69" t="n">
-        <v>0.4938911673985256</v>
+        <v>0.4819853642097298</v>
       </c>
       <c r="M69" t="n">
-        <v>-6.641046291158119</v>
+        <v>-3.261918459386246</v>
       </c>
       <c r="N69" t="n">
-        <v>-30.85488102411852</v>
+        <v>-27.66594526668528</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -8687,12 +8959,12 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>16P-755</t>
         </is>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -8702,48 +8974,52 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>592172</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>8</v>
-      </c>
-      <c r="D70" t="n">
-        <v>4933</v>
+          <t>592351</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>4933</t>
+        </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Alchornea lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.4777</v>
+        <v>0.5078</v>
       </c>
       <c r="H70" t="n">
-        <v>27.89</v>
+        <v>30.78</v>
       </c>
       <c r="I70" t="n">
-        <v>44.83</v>
+        <v>43.51</v>
       </c>
       <c r="J70" t="n">
-        <v>-29.25</v>
+        <v>-26.51</v>
       </c>
       <c r="K70" t="n">
-        <v>0.01145344039013863</v>
+        <v>0.008428783054762122</v>
       </c>
       <c r="L70" t="n">
-        <v>0.4938911673985256</v>
+        <v>0.4687094144720008</v>
       </c>
       <c r="M70" t="n">
-        <v>-6.641046291158119</v>
+        <v>-4.809842286515277</v>
       </c>
       <c r="N70" t="n">
-        <v>-30.85488102411852</v>
+        <v>-30.10625891033084</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -8806,12 +9082,12 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>17C-4933</t>
         </is>
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -8821,14 +9097,18 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>592124</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>6</v>
-      </c>
-      <c r="D71" t="n">
-        <v>410</v>
+          <t>592172</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -8837,32 +9117,32 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.4588</v>
+        <v>0.4875</v>
       </c>
       <c r="H71" t="n">
-        <v>31.51</v>
+        <v>28.73</v>
       </c>
       <c r="I71" t="n">
-        <v>46.68</v>
+        <v>44.83</v>
       </c>
       <c r="J71" t="n">
-        <v>-27.4</v>
+        <v>-29.25</v>
       </c>
       <c r="K71" t="n">
-        <v>0.01205693768572095</v>
+        <v>0.01145344039013863</v>
       </c>
       <c r="L71" t="n">
-        <v>0.4900114968232365</v>
+        <v>0.4938911673985256</v>
       </c>
       <c r="M71" t="n">
-        <v>-3.788010217626178</v>
+        <v>-6.641046291158119</v>
       </c>
       <c r="N71" t="n">
-        <v>-30.18403783124384</v>
+        <v>-30.85488102411852</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -8925,12 +9205,12 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>8P-410</t>
         </is>
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -8940,14 +9220,18 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>592118</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>6</v>
-      </c>
-      <c r="D72" t="n">
-        <v>410</v>
+          <t>592172</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -8956,30 +9240,32 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="H72" t="inlineStr"/>
+        <v>0.4777</v>
+      </c>
+      <c r="H72" t="n">
+        <v>27.89</v>
+      </c>
       <c r="I72" t="n">
-        <v>44.43</v>
+        <v>44.83</v>
       </c>
       <c r="J72" t="n">
-        <v>-27.46</v>
+        <v>-29.25</v>
       </c>
       <c r="K72" t="n">
-        <v>0.01234451153346652</v>
+        <v>0.01145344039013863</v>
       </c>
       <c r="L72" t="n">
-        <v>0.4921002145511302</v>
+        <v>0.4938911673985256</v>
       </c>
       <c r="M72" t="n">
-        <v>-3.45414429412776</v>
+        <v>-6.641046291158119</v>
       </c>
       <c r="N72" t="n">
-        <v>-30.37848513352635</v>
+        <v>-30.85488102411852</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -9042,12 +9328,12 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>8P-410</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -9057,46 +9343,52 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>592097</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>4</v>
-      </c>
-      <c r="D73" t="n">
-        <v>310</v>
+          <t>592124</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Myrcia sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.9681</v>
-      </c>
-      <c r="H73" t="inlineStr"/>
+        <v>0.4588</v>
+      </c>
+      <c r="H73" t="n">
+        <v>31.51</v>
+      </c>
       <c r="I73" t="n">
-        <v>43.26</v>
+        <v>46.68</v>
       </c>
       <c r="J73" t="n">
-        <v>-28.05</v>
+        <v>-27.4</v>
       </c>
       <c r="K73" t="n">
-        <v>0.009234656882224123</v>
+        <v>0.01205693768572095</v>
       </c>
       <c r="L73" t="n">
-        <v>0.4662536017268455</v>
+        <v>0.4900114968232365</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.966923362180259</v>
+        <v>-3.788010217626178</v>
       </c>
       <c r="N73" t="n">
-        <v>-31.12710724731404</v>
+        <v>-30.18403783124384</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -9159,12 +9451,12 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>6N-310</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -9174,48 +9466,50 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>592235</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>11</v>
-      </c>
-      <c r="D74" t="n">
-        <v>290</v>
+          <t>592118</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Myrcia sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.4759</v>
-      </c>
-      <c r="H74" t="n">
-        <v>29.6</v>
-      </c>
+        <v>0.0005</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
-        <v>43.23</v>
+        <v>44.43</v>
       </c>
       <c r="J74" t="n">
-        <v>-27.08</v>
+        <v>-27.46</v>
       </c>
       <c r="K74" t="n">
-        <v>0.008734567321107571</v>
+        <v>0.01234451153346652</v>
       </c>
       <c r="L74" t="n">
-        <v>0.4636941617791257</v>
+        <v>0.4921002145511302</v>
       </c>
       <c r="M74" t="n">
-        <v>-3.332738503764699</v>
+        <v>-3.45414429412776</v>
       </c>
       <c r="N74" t="n">
-        <v>-30.54376534046649</v>
+        <v>-30.37848513352635</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -9278,12 +9572,12 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>6N-290</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -9293,14 +9587,18 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>592123</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>6</v>
-      </c>
-      <c r="D75" t="n">
-        <v>200</v>
+          <t>592097</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -9309,32 +9607,30 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.4915</v>
-      </c>
-      <c r="H75" t="n">
-        <v>32.32</v>
-      </c>
+        <v>0.9681</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
-        <v>41.44</v>
+        <v>43.26</v>
       </c>
       <c r="J75" t="n">
-        <v>-28.28</v>
+        <v>-28.05</v>
       </c>
       <c r="K75" t="n">
-        <v>0.01050205454647201</v>
+        <v>0.009234656882224123</v>
       </c>
       <c r="L75" t="n">
-        <v>0.47469435072868</v>
+        <v>0.4662536017268455</v>
       </c>
       <c r="M75" t="n">
-        <v>-3.008989729463202</v>
+        <v>-1.966923362180259</v>
       </c>
       <c r="N75" t="n">
-        <v>-31.8660069959876</v>
+        <v>-31.12710724731404</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -9397,12 +9693,12 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>4NP-200</t>
         </is>
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -9412,14 +9708,18 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>592107</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>4</v>
-      </c>
-      <c r="D76" t="n">
-        <v>915</v>
+          <t>592235</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>915</t>
+        </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -9428,32 +9728,32 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.5107</v>
+        <v>0.4759</v>
       </c>
       <c r="H76" t="n">
-        <v>30.49</v>
+        <v>29.6</v>
       </c>
       <c r="I76" t="n">
-        <v>42.17</v>
+        <v>43.23</v>
       </c>
       <c r="J76" t="n">
-        <v>-27.5</v>
+        <v>-27.08</v>
       </c>
       <c r="K76" t="n">
-        <v>0.009755838734878302</v>
+        <v>0.008734567321107571</v>
       </c>
       <c r="L76" t="n">
-        <v>0.469908053711939</v>
+        <v>0.4636941617791257</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.91633761619565</v>
+        <v>-3.332738503764699</v>
       </c>
       <c r="N76" t="n">
-        <v>-30.81599156366202</v>
+        <v>-30.54376534046649</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -9516,12 +9816,12 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>11P-915</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -9531,48 +9831,52 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>592108</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>4</v>
-      </c>
-      <c r="D77" t="n">
-        <v>4905</v>
+          <t>592123</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>4905</t>
+        </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Alchornea lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.4492</v>
+        <v>0.4915</v>
       </c>
       <c r="H77" t="n">
-        <v>30.12</v>
+        <v>32.32</v>
       </c>
       <c r="I77" t="n">
-        <v>46.38</v>
+        <v>41.44</v>
       </c>
       <c r="J77" t="n">
-        <v>-25.91</v>
+        <v>-28.28</v>
       </c>
       <c r="K77" t="n">
-        <v>0.01181127928365552</v>
+        <v>0.01050205454647201</v>
       </c>
       <c r="L77" t="n">
-        <v>0.5033288720554695</v>
+        <v>0.47469435072868</v>
       </c>
       <c r="M77" t="n">
-        <v>-3.180981265810872</v>
+        <v>-3.008989729463202</v>
       </c>
       <c r="N77" t="n">
-        <v>-27.86039256896779</v>
+        <v>-31.8660069959876</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -9635,12 +9939,12 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>6N-4905</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -9650,48 +9954,52 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>592055</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>2</v>
-      </c>
-      <c r="D78" t="n">
-        <v>5807</v>
+          <t>592107</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>5807</t>
+        </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Alchornea lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.4685</v>
+        <v>0.5107</v>
       </c>
       <c r="H78" t="n">
-        <v>30.55</v>
+        <v>30.49</v>
       </c>
       <c r="I78" t="n">
-        <v>45.56</v>
+        <v>42.17</v>
       </c>
       <c r="J78" t="n">
-        <v>-25.48</v>
+        <v>-27.5</v>
       </c>
       <c r="K78" t="n">
-        <v>0.01132223388433968</v>
+        <v>0.009755838734878302</v>
       </c>
       <c r="L78" t="n">
-        <v>0.4808545087152221</v>
+        <v>0.469908053711939</v>
       </c>
       <c r="M78" t="n">
-        <v>-4.59738215337992</v>
+        <v>-1.91633761619565</v>
       </c>
       <c r="N78" t="n">
-        <v>-28.2395648084187</v>
+        <v>-30.81599156366202</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -9754,12 +10062,12 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>4NP-5807</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -9769,14 +10077,18 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>592277</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>13</v>
-      </c>
-      <c r="D79" t="n">
-        <v>219</v>
+          <t>592108</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -9785,32 +10097,32 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.4857</v>
+        <v>0.4492</v>
       </c>
       <c r="H79" t="n">
-        <v>28.88</v>
+        <v>30.12</v>
       </c>
       <c r="I79" t="n">
-        <v>44.62</v>
+        <v>46.38</v>
       </c>
       <c r="J79" t="n">
-        <v>-26.35</v>
+        <v>-25.91</v>
       </c>
       <c r="K79" t="n">
-        <v>0.01293638020438906</v>
+        <v>0.01181127928365552</v>
       </c>
       <c r="L79" t="n">
-        <v>0.496847737832237</v>
+        <v>0.5033288720554695</v>
       </c>
       <c r="M79" t="n">
-        <v>0.2284980135517662</v>
+        <v>-3.180981265810872</v>
       </c>
       <c r="N79" t="n">
-        <v>-29.00763165243463</v>
+        <v>-27.86039256896779</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -9873,12 +10185,12 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>4NP-219</t>
         </is>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -9888,14 +10200,18 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>592117</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>6</v>
-      </c>
-      <c r="D80" t="n">
-        <v>267</v>
+          <t>592055</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -9904,32 +10220,32 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.4403</v>
+        <v>0.4685</v>
       </c>
       <c r="H80" t="n">
-        <v>30.16</v>
+        <v>30.55</v>
       </c>
       <c r="I80" t="n">
-        <v>46.68</v>
+        <v>45.56</v>
       </c>
       <c r="J80" t="n">
-        <v>-28.01</v>
+        <v>-25.48</v>
       </c>
       <c r="K80" t="n">
-        <v>0.0113792582413897</v>
+        <v>0.01132223388433968</v>
       </c>
       <c r="L80" t="n">
-        <v>0.4697320406963792</v>
+        <v>0.4808545087152221</v>
       </c>
       <c r="M80" t="n">
-        <v>-2.381726479254052</v>
+        <v>-4.59738215337992</v>
       </c>
       <c r="N80" t="n">
-        <v>-30.68960081717838</v>
+        <v>-28.2395648084187</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -9992,12 +10308,12 @@
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>2P-267</t>
         </is>
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -10007,14 +10323,18 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>592250</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>12</v>
-      </c>
-      <c r="D81" t="n">
-        <v>642</v>
+          <t>592277</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -10023,32 +10343,32 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.4675</v>
+        <v>0.4857</v>
       </c>
       <c r="H81" t="n">
-        <v>31.74</v>
+        <v>28.88</v>
       </c>
       <c r="I81" t="n">
-        <v>44.63</v>
+        <v>44.62</v>
       </c>
       <c r="J81" t="n">
-        <v>-25.22</v>
+        <v>-26.35</v>
       </c>
       <c r="K81" t="n">
-        <v>0.01226143391535393</v>
+        <v>0.01293638020438906</v>
       </c>
       <c r="L81" t="n">
-        <v>0.4982738719029886</v>
+        <v>0.496847737832237</v>
       </c>
       <c r="M81" t="n">
-        <v>-4.465859213819937</v>
+        <v>0.2284980135517662</v>
       </c>
       <c r="N81" t="n">
-        <v>-28.08400696659269</v>
+        <v>-29.00763165243463</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -10111,12 +10431,12 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>13N-642</t>
         </is>
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -10126,14 +10446,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>592148</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>7</v>
-      </c>
-      <c r="D82" t="n">
-        <v>286</v>
+          <t>592117</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -10142,32 +10466,32 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.4504</v>
+        <v>0.4403</v>
       </c>
       <c r="H82" t="n">
-        <v>30.38</v>
+        <v>30.16</v>
       </c>
       <c r="I82" t="n">
-        <v>46.18</v>
+        <v>46.68</v>
       </c>
       <c r="J82" t="n">
-        <v>-26.33</v>
+        <v>-28.01</v>
       </c>
       <c r="K82" t="n">
-        <v>0.01274017254269937</v>
+        <v>0.0113792582413897</v>
       </c>
       <c r="L82" t="n">
-        <v>0.4852329734163069</v>
+        <v>0.4697320406963792</v>
       </c>
       <c r="M82" t="n">
-        <v>-7.61229261406261</v>
+        <v>-2.381726479254052</v>
       </c>
       <c r="N82" t="n">
-        <v>-29.2604131454019</v>
+        <v>-30.68960081717838</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -10230,12 +10554,12 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>6N-286</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -10245,14 +10569,18 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>592015</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>1</v>
-      </c>
-      <c r="D83" t="n">
-        <v>7594</v>
+          <t>592250</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>7594</t>
+        </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -10265,28 +10593,28 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.468</v>
+        <v>0.4675</v>
       </c>
       <c r="H83" t="n">
-        <v>29.32</v>
+        <v>31.74</v>
       </c>
       <c r="I83" t="n">
-        <v>46.71</v>
+        <v>44.63</v>
       </c>
       <c r="J83" t="n">
-        <v>-25.61</v>
+        <v>-25.22</v>
       </c>
       <c r="K83" t="n">
-        <v>0.0115013147237653</v>
+        <v>0.01226143391535393</v>
       </c>
       <c r="L83" t="n">
-        <v>0.4983644294167911</v>
+        <v>0.4982738719029886</v>
       </c>
       <c r="M83" t="n">
-        <v>-4.455742064623015</v>
+        <v>-4.465859213819937</v>
       </c>
       <c r="N83" t="n">
-        <v>-28.2006753479622</v>
+        <v>-28.08400696659269</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -10349,12 +10677,12 @@
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>12C-7594</t>
         </is>
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -10364,14 +10692,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>592133</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>7</v>
-      </c>
-      <c r="D84" t="n">
-        <v>6994</v>
+          <t>592148</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>6994</t>
+        </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -10384,28 +10716,28 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.4614</v>
+        <v>0.4504</v>
       </c>
       <c r="H84" t="n">
-        <v>29.76</v>
+        <v>30.38</v>
       </c>
       <c r="I84" t="n">
-        <v>45.09</v>
+        <v>46.18</v>
       </c>
       <c r="J84" t="n">
-        <v>-27.27</v>
+        <v>-26.33</v>
       </c>
       <c r="K84" t="n">
-        <v>0.0106074030008212</v>
+        <v>0.01274017254269937</v>
       </c>
       <c r="L84" t="n">
-        <v>0.4836745282750483</v>
+        <v>0.4852329734163069</v>
       </c>
       <c r="M84" t="n">
-        <v>-5.265114000376758</v>
+        <v>-7.61229261406261</v>
       </c>
       <c r="N84" t="n">
-        <v>-29.95070106850483</v>
+        <v>-29.2604131454019</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -10468,12 +10800,12 @@
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>7C-6994</t>
         </is>
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -10483,48 +10815,52 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>592286</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>13</v>
-      </c>
-      <c r="D85" t="n">
-        <v>92</v>
+          <t>592015</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Myrcia sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.5299</v>
+        <v>0.468</v>
       </c>
       <c r="H85" t="n">
-        <v>31.37</v>
+        <v>29.32</v>
       </c>
       <c r="I85" t="n">
-        <v>42.33</v>
+        <v>46.71</v>
       </c>
       <c r="J85" t="n">
-        <v>-26.51</v>
+        <v>-25.61</v>
       </c>
       <c r="K85" t="n">
-        <v>0.01024325152877396</v>
+        <v>0.0115013147237653</v>
       </c>
       <c r="L85" t="n">
-        <v>0.4720974145093479</v>
+        <v>0.4983644294167911</v>
       </c>
       <c r="M85" t="n">
-        <v>-2.493015120420191</v>
+        <v>-4.455742064623015</v>
       </c>
       <c r="N85" t="n">
-        <v>-30.30070621261335</v>
+        <v>-28.2006753479622</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -10587,12 +10923,12 @@
       </c>
       <c r="AH85" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>1C-92</t>
         </is>
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -10602,14 +10938,18 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>592079</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>3</v>
-      </c>
-      <c r="D86" t="n">
-        <v>335</v>
+          <t>592133</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -10618,32 +10958,32 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0.4709</v>
+        <v>0.4614</v>
       </c>
       <c r="H86" t="n">
-        <v>29.85</v>
+        <v>29.76</v>
       </c>
       <c r="I86" t="n">
-        <v>46.14</v>
+        <v>45.09</v>
       </c>
       <c r="J86" t="n">
-        <v>-25.44</v>
+        <v>-27.27</v>
       </c>
       <c r="K86" t="n">
-        <v>0.01561967084759183</v>
+        <v>0.0106074030008212</v>
       </c>
       <c r="L86" t="n">
-        <v>0.4873678341481503</v>
+        <v>0.4836745282750483</v>
       </c>
       <c r="M86" t="n">
-        <v>-0.2368908495066354</v>
+        <v>-5.265114000376758</v>
       </c>
       <c r="N86" t="n">
-        <v>-27.98678331545143</v>
+        <v>-29.95070106850483</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -10706,12 +11046,12 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>7C-335</t>
         </is>
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -10721,48 +11061,52 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>592019</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>1</v>
-      </c>
-      <c r="D87" t="n">
-        <v>9742</v>
+          <t>592286</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>9742</t>
+        </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Alchornea lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>0.4743</v>
+        <v>0.5299</v>
       </c>
       <c r="H87" t="n">
-        <v>29.4</v>
+        <v>31.37</v>
       </c>
       <c r="I87" t="n">
-        <v>43.58</v>
+        <v>42.33</v>
       </c>
       <c r="J87" t="n">
-        <v>-27.02</v>
+        <v>-26.51</v>
       </c>
       <c r="K87" t="n">
-        <v>0.01311436575870028</v>
+        <v>0.01024325152877396</v>
       </c>
       <c r="L87" t="n">
-        <v>0.4914807959170675</v>
+        <v>0.4720974145093479</v>
       </c>
       <c r="M87" t="n">
-        <v>-5.770971460222846</v>
+        <v>-2.493015120420191</v>
       </c>
       <c r="N87" t="n">
-        <v>-29.73680903599406</v>
+        <v>-30.30070621261335</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -10825,12 +11169,12 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>13N-9742</t>
         </is>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -10840,14 +11184,18 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>592103</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>4</v>
-      </c>
-      <c r="D88" t="n">
-        <v>155</v>
+          <t>592079</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -10856,32 +11204,32 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.4691</v>
+        <v>0.4709</v>
       </c>
       <c r="H88" t="n">
-        <v>30.63</v>
+        <v>29.85</v>
       </c>
       <c r="I88" t="n">
-        <v>44.94</v>
+        <v>46.14</v>
       </c>
       <c r="J88" t="n">
-        <v>-25.28</v>
+        <v>-25.44</v>
       </c>
       <c r="K88" t="n">
-        <v>0.01074738152556895</v>
+        <v>0.01561967084759183</v>
       </c>
       <c r="L88" t="n">
-        <v>0.4933109900764689</v>
+        <v>0.4873678341481503</v>
       </c>
       <c r="M88" t="n">
-        <v>-2.71559240275247</v>
+        <v>-0.2368908495066354</v>
       </c>
       <c r="N88" t="n">
-        <v>-28.2006753479622</v>
+        <v>-27.98678331545143</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -10944,12 +11292,12 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>3N-155</t>
         </is>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -10959,48 +11307,52 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>592294</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>14</v>
-      </c>
-      <c r="D89" t="n">
-        <v>101</v>
+          <t>592019</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Myrcia sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.5019</v>
+        <v>0.4743</v>
       </c>
       <c r="H89" t="n">
-        <v>30.78</v>
+        <v>29.4</v>
       </c>
       <c r="I89" t="n">
-        <v>42.65</v>
+        <v>43.58</v>
       </c>
       <c r="J89" t="n">
-        <v>-26.45</v>
+        <v>-27.02</v>
       </c>
       <c r="K89" t="n">
-        <v>0.009604069192232665</v>
+        <v>0.01311436575870028</v>
       </c>
       <c r="L89" t="n">
-        <v>0.4552478286555752</v>
+        <v>0.4914807959170675</v>
       </c>
       <c r="M89" t="n">
-        <v>-0.6415768173835065</v>
+        <v>-5.770971460222846</v>
       </c>
       <c r="N89" t="n">
-        <v>-29.88264451270594</v>
+        <v>-29.73680903599406</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -11063,12 +11415,12 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>1C-101</t>
         </is>
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -11078,14 +11430,18 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>592091</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>4</v>
-      </c>
-      <c r="D90" t="n">
-        <v>209</v>
+          <t>592103</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -11098,28 +11454,28 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.4746</v>
+        <v>0.4691</v>
       </c>
       <c r="H90" t="n">
-        <v>27.48</v>
+        <v>30.63</v>
       </c>
       <c r="I90" t="n">
-        <v>43.76</v>
+        <v>44.94</v>
       </c>
       <c r="J90" t="n">
-        <v>-27.79</v>
+        <v>-25.28</v>
       </c>
       <c r="K90" t="n">
-        <v>0.01057256570554311</v>
+        <v>0.01074738152556895</v>
       </c>
       <c r="L90" t="n">
-        <v>0.4730384938999251</v>
+        <v>0.4933109900764689</v>
       </c>
       <c r="M90" t="n">
-        <v>-3.221449862598559</v>
+        <v>-2.71559240275247</v>
       </c>
       <c r="N90" t="n">
-        <v>-29.87292214759182</v>
+        <v>-28.2006753479622</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -11182,12 +11538,12 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>4NP-209</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -11197,14 +11553,18 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>592302</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>14</v>
-      </c>
-      <c r="D91" t="n">
-        <v>666</v>
+          <t>592294</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -11217,28 +11577,28 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.4851</v>
+        <v>0.5019</v>
       </c>
       <c r="H91" t="n">
-        <v>31.65</v>
+        <v>30.78</v>
       </c>
       <c r="I91" t="n">
-        <v>42.21</v>
+        <v>42.65</v>
       </c>
       <c r="J91" t="n">
-        <v>-27.34</v>
+        <v>-26.45</v>
       </c>
       <c r="K91" t="n">
-        <v>0.01049533699276146</v>
+        <v>0.009604069192232665</v>
       </c>
       <c r="L91" t="n">
-        <v>0.4621550578712807</v>
+        <v>0.4552478286555752</v>
       </c>
       <c r="M91" t="n">
-        <v>-0.8338026521250202</v>
+        <v>-0.6415768173835065</v>
       </c>
       <c r="N91" t="n">
-        <v>-30.82571392877614</v>
+        <v>-29.88264451270594</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -11301,12 +11661,12 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>14NP-666</t>
         </is>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -11316,48 +11676,52 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>592272</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>13</v>
-      </c>
-      <c r="D92" t="n">
-        <v>188</v>
+          <t>592091</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Myrcia sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>0.5074</v>
+        <v>0.4746</v>
       </c>
       <c r="H92" t="n">
-        <v>32.4</v>
+        <v>27.48</v>
       </c>
       <c r="I92" t="n">
-        <v>42.42</v>
+        <v>43.76</v>
       </c>
       <c r="J92" t="n">
-        <v>-26.55</v>
+        <v>-27.79</v>
       </c>
       <c r="K92" t="n">
-        <v>0.008709543922876754</v>
+        <v>0.01057256570554311</v>
       </c>
       <c r="L92" t="n">
-        <v>0.4720636233608297</v>
+        <v>0.4730384938999251</v>
       </c>
       <c r="M92" t="n">
-        <v>-2.513249418814035</v>
+        <v>-3.221449862598559</v>
       </c>
       <c r="N92" t="n">
-        <v>-30.30070621261335</v>
+        <v>-29.87292214759182</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -11420,12 +11784,12 @@
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>4NP-188</t>
         </is>
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
@@ -11435,48 +11799,52 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>592029</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>1</v>
-      </c>
-      <c r="D93" t="n">
-        <v>685</v>
+          <t>592302</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Alchornea lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>0.467</v>
+        <v>0.4851</v>
       </c>
       <c r="H93" t="n">
-        <v>30.66</v>
+        <v>31.65</v>
       </c>
       <c r="I93" t="n">
-        <v>46</v>
+        <v>42.21</v>
       </c>
       <c r="J93" t="n">
-        <v>-27.31</v>
+        <v>-27.34</v>
       </c>
       <c r="K93" t="n">
-        <v>0.01267967812432159</v>
+        <v>0.01049533699276146</v>
       </c>
       <c r="L93" t="n">
-        <v>0.4994272096638095</v>
+        <v>0.4621550578712807</v>
       </c>
       <c r="M93" t="n">
-        <v>-4.344453423456875</v>
+        <v>-0.8338026521250202</v>
       </c>
       <c r="N93" t="n">
-        <v>-29.62986301973867</v>
+        <v>-30.82571392877614</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -11539,12 +11907,12 @@
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>14NP-685</t>
         </is>
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -11554,14 +11922,18 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>592291</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>14</v>
-      </c>
-      <c r="D94" t="n">
-        <v>627</v>
+          <t>592272</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -11570,32 +11942,32 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0.5173</v>
+        <v>0.5074</v>
       </c>
       <c r="H94" t="n">
-        <v>30.58</v>
+        <v>32.4</v>
       </c>
       <c r="I94" t="n">
-        <v>41.34</v>
+        <v>42.42</v>
       </c>
       <c r="J94" t="n">
-        <v>-28.62</v>
+        <v>-26.55</v>
       </c>
       <c r="K94" t="n">
-        <v>0.01074976244852566</v>
+        <v>0.008709543922876754</v>
       </c>
       <c r="L94" t="n">
-        <v>0.4599060835667828</v>
+        <v>0.4720636233608297</v>
       </c>
       <c r="M94" t="n">
-        <v>-1.22837147080497</v>
+        <v>-2.513249418814035</v>
       </c>
       <c r="N94" t="n">
-        <v>-31.63267023324858</v>
+        <v>-30.30070621261335</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -11658,12 +12030,12 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>13N-627</t>
         </is>
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>sp nov</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
     </row>
@@ -11673,14 +12045,18 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>592158</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>8</v>
-      </c>
-      <c r="D95" t="n">
-        <v>9091</v>
+          <t>592029</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -11689,28 +12065,32 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0.4092</v>
+        <v>0.467</v>
       </c>
       <c r="H95" t="n">
-        <v>30.39</v>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+        <v>30.66</v>
+      </c>
+      <c r="I95" t="n">
+        <v>46</v>
+      </c>
+      <c r="J95" t="n">
+        <v>-27.31</v>
+      </c>
       <c r="K95" t="n">
-        <v>0.01066420688163546</v>
+        <v>0.01267967812432159</v>
       </c>
       <c r="L95" t="n">
-        <v>0.4858526442003956</v>
+        <v>0.4994272096638095</v>
       </c>
       <c r="M95" t="n">
-        <v>-5.477574133512115</v>
+        <v>-4.344453423456875</v>
       </c>
       <c r="N95" t="n">
-        <v>-28.06456223636443</v>
+        <v>-29.62986301973867</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -11773,12 +12153,254 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>1C-9091</t>
         </is>
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>lojaensis</t>
+          <t>Alchornea lojaensis</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>592291</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Myrcia sp nov</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>NP</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>0.5173</v>
+      </c>
+      <c r="H96" t="n">
+        <v>30.58</v>
+      </c>
+      <c r="I96" t="n">
+        <v>41.34</v>
+      </c>
+      <c r="J96" t="n">
+        <v>-28.62</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0.01074976244852566</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.4599060835667828</v>
+      </c>
+      <c r="M96" t="n">
+        <v>-1.22837147080497</v>
+      </c>
+      <c r="N96" t="n">
+        <v>-31.63267023324858</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>SFNu</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="n">
+        <v>45288</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>20</v>
+      </c>
+      <c r="R96" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="S96" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="T96" t="n">
+        <v>466.0314830157415</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0.4788333333333334</v>
+      </c>
+      <c r="V96" t="n">
+        <v>1.432925004304031</v>
+      </c>
+      <c r="W96" t="n">
+        <v>478.92372</v>
+      </c>
+      <c r="X96" t="n">
+        <v>12.41631</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>0.579333851742069</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>0.1048880165242109</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>0.9568198217758509</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>0.03127609545374357</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>2.282922889183617</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>1.342235834509844</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>413.538</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>14NP-659</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>Myrcia sp nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>592158</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>7237</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Alchornea lojaensis</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>0.4092</v>
+      </c>
+      <c r="H97" t="n">
+        <v>30.39</v>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="n">
+        <v>0.01066420688163546</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.4858526442003956</v>
+      </c>
+      <c r="M97" t="n">
+        <v>-5.477574133512115</v>
+      </c>
+      <c r="N97" t="n">
+        <v>-28.06456223636443</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>SFNu</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="n">
+        <v>45276</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>20</v>
+      </c>
+      <c r="R97" t="n">
+        <v>44.74</v>
+      </c>
+      <c r="S97" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="T97" t="n">
+        <v>437.4161823871256</v>
+      </c>
+      <c r="U97" t="n">
+        <v>0.6288333333333332</v>
+      </c>
+      <c r="V97" t="n">
+        <v>2.043814727538423</v>
+      </c>
+      <c r="W97" t="n">
+        <v>512.3241399999999</v>
+      </c>
+      <c r="X97" t="n">
+        <v>12.00725</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>1.336143849681799</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>0.003011286638273465</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>5.019103663996447</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>0.02524274359324394</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>3.684415272404858</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>2.878739574713596</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>0.7703790828992938</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>576.953</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>8P-7237</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
     </row>
